--- a/docs/screenshot-index.xlsx
+++ b/docs/screenshot-index.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="772">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="800">
   <si>
     <t>#</t>
   </si>
@@ -50,228 +50,231 @@
     <t>1 — Essential</t>
   </si>
   <si>
+    <t>Captured</t>
+  </si>
+  <si>
+    <t>bom/mode.png</t>
+  </si>
+  <si>
+    <t>Bill of materials mode</t>
+  </si>
+  <si>
+    <t>The editor with the automatically computed rows filled in, all five column headers readable, and the mode banner above the table.</t>
+  </si>
+  <si>
+    <t>Generate a layout, then switch the bill of materials button on.</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>/docs/bom/overview</t>
+  </si>
+  <si>
+    <t>The bill of materials editor with its five columns filled from the layout — line number, material description, quantity, unit and remark.</t>
+  </si>
+  <si>
+    <t>bom-mode</t>
+  </si>
+  <si>
+    <t>bom/template-window.png</t>
+  </si>
+  <si>
+    <t>A template beside the plant list</t>
+  </si>
+  <si>
+    <t>Both windows visible at once: the template in its own window and the automatic list behind it, so the side-by-side relationship is clear.</t>
+  </si>
+  <si>
+    <t>In bill of materials mode, pick a template and load it. Arrange the two windows so both are readable.</t>
+  </si>
+  <si>
+    <t>Label which window is the template and which is the plant list.</t>
+  </si>
+  <si>
+    <t>/docs/bom/templates</t>
+  </si>
+  <si>
+    <t>A template opened in its own window next to the automatically computed bill of materials.</t>
+  </si>
+  <si>
+    <t>bom-template-window</t>
+  </si>
+  <si>
+    <t>editing/pile-dialog.png</t>
+  </si>
+  <si>
+    <t>Pile layout editor</t>
+  </si>
+  <si>
+    <t>The editor with several piles placed on the reference table, the drawing on one side and the coordinate table on the other.</t>
+  </si>
+  <si>
+    <t>Generate a layout, then switch the piles button on for the first time, or use Edit-Pile ▸ Define Pile Layout…</t>
+  </si>
+  <si>
+    <t>Mark the table's bottom-left corner as the origin and label the two axis directions.</t>
+  </si>
+  <si>
+    <t>/docs/editing/piles</t>
+  </si>
+  <si>
+    <t>The pile layout editor showing one reference table with piles placed on it and the coordinate table beside it.</t>
+  </si>
+  <si>
+    <t>pile-dialog</t>
+  </si>
+  <si>
+    <t>editing/piles-overlay.png</t>
+  </si>
+  <si>
+    <t>Piles with the layout switched off</t>
+  </si>
+  <si>
+    <t>A zoomed plot view with the pile overlay on and Plant Layout off, so nothing but the piles is drawn, each one labelled with its coordinates.</t>
+  </si>
+  <si>
+    <t>Define a pile pattern, keep the piles button on, switch Plant Layout off, then zoom into a block of tables.</t>
+  </si>
+  <si>
+    <t>A close view of the pile positions with the plant layout switched off, each pile carrying its easting and northing.</t>
+  </si>
+  <si>
+    <t>piles-overlay</t>
+  </si>
+  <si>
+    <t>editing/sketch-palette.png</t>
+  </si>
+  <si>
+    <t>The sketch tool palette</t>
+  </si>
+  <si>
+    <t>The full palette with every tool button label readable, including the snap, orthogonal, grid, undo and redo controls and the layer row.</t>
+  </si>
+  <si>
+    <t>Generate a layout, then switch Sketch Mode on. Capture the palette area of the panel; stitch if it does not fit.</t>
+  </si>
+  <si>
+    <t>Group the buttons and label the groups: select and edit, place, draw, annotate, trenches, navigate.</t>
+  </si>
+  <si>
+    <t>/docs/editing/sketch-mode</t>
+  </si>
+  <si>
+    <t>The sketch mode tool palette showing every drawing and editing tool.</t>
+  </si>
+  <si>
+    <t>sketch-palette</t>
+  </si>
+  <si>
+    <t>editing/sketch-selection.png</t>
+  </si>
+  <si>
+    <t>Selecting several tables</t>
+  </si>
+  <si>
+    <t>A zoomed plot view with a group of tables highlighted in the selection colour, ideally mid rubber-band so the selection rectangle is visible too.</t>
+  </si>
+  <si>
+    <t>In Sketch Mode with the move tool active, drag on empty space across a group of tables.</t>
+  </si>
+  <si>
+    <t>Outline the rubber-band rectangle.</t>
+  </si>
+  <si>
+    <t>Several tables highlighted as a selection after a rubber-band drag.</t>
+  </si>
+  <si>
+    <t>sketch-selection</t>
+  </si>
+  <si>
+    <t>energy/buttons.png</t>
+  </si>
+  <si>
+    <t>Energy controls</t>
+  </si>
+  <si>
+    <t>The energy button block: Calculate Energy, Show Energy Chart, the export button and its interval selector, plus the status line.</t>
+  </si>
+  <si>
+    <t>After a layout has been generated, so the buttons are enabled.</t>
+  </si>
+  <si>
+    <t>/docs/energy/overview</t>
+  </si>
+  <si>
+    <t>The Calculate Energy, Show Energy Chart and Export controls with the interval selector.</t>
+  </si>
+  <si>
+    <t>energy-buttons</t>
+  </si>
+  <si>
+    <t>energy/chart-daily.png</t>
+  </si>
+  <si>
+    <t>Daily energy and irradiance</t>
+  </si>
+  <si>
+    <t>The daily view with both charts drawn, the day slider visible, and the crosshair active so the readout strip shows values.</t>
+  </si>
+  <si>
+    <t>Calculate energy, click Show Energy Chart, and hover the pointer over the middle of the day.</t>
+  </si>
+  <si>
+    <t>Label the two charts and the day slider.</t>
+  </si>
+  <si>
+    <t>/docs/energy/timeseries</t>
+  </si>
+  <si>
+    <t>The daily chart with hourly energy bars above hourly irradiance bars, a day slider and a crosshair readout.</t>
+  </si>
+  <si>
+    <t>energy-chart-daily</t>
+  </si>
+  <si>
+    <t>energy/chart-monthly.png</t>
+  </si>
+  <si>
+    <t>Monthly energy and irradiance</t>
+  </si>
+  <si>
+    <t>The monthly view with all twelve months and the annual totals visible.</t>
+  </si>
+  <si>
+    <t>In the energy chart window, switch to the monthly view.</t>
+  </si>
+  <si>
+    <t>The monthly chart with twelve energy bars and twelve irradiance bars, plus the annual totals.</t>
+  </si>
+  <si>
+    <t>energy-chart-monthly</t>
+  </si>
+  <si>
+    <t>energy/degradation-pvalues.png</t>
+  </si>
+  <si>
+    <t>Degradation and probability settings</t>
+  </si>
+  <si>
+    <t>Both sections together: first-year and annual degradation, plant lifetime, combined uncertainty, and the three exceedance probability fields.</t>
+  </si>
+  <si>
+    <t>Nothing changed from defaults.</t>
+  </si>
+  <si>
+    <t>/docs/energy/lifetime-and-p-values</t>
+  </si>
+  <si>
+    <t>The degradation and probabilistic yield sections with their default values.</t>
+  </si>
+  <si>
+    <t>energy-degradation-pvalues</t>
+  </si>
+  <si>
     <t>Pending</t>
   </si>
   <si>
-    <t>bom/mode.png</t>
-  </si>
-  <si>
-    <t>Bill of materials mode</t>
-  </si>
-  <si>
-    <t>The editor with the automatically computed rows filled in, all five column headers readable, and the add, delete, rebuild and export controls visible.</t>
-  </si>
-  <si>
-    <t>Generate a layout, then switch the bill of materials button on.</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>/docs/bom/overview</t>
-  </si>
-  <si>
-    <t>The bill of materials editor with its five columns filled from the layout, and the row and export controls.</t>
-  </si>
-  <si>
-    <t>bom-mode</t>
-  </si>
-  <si>
-    <t>bom/template-window.png</t>
-  </si>
-  <si>
-    <t>A template beside the plant list</t>
-  </si>
-  <si>
-    <t>Both windows visible at once: the template in its own window and the automatic list behind it, so the side-by-side relationship is clear.</t>
-  </si>
-  <si>
-    <t>In bill of materials mode, pick a template and load it. Arrange the two windows so both are readable.</t>
-  </si>
-  <si>
-    <t>Label which window is the template and which is the plant list.</t>
-  </si>
-  <si>
-    <t>/docs/bom/templates</t>
-  </si>
-  <si>
-    <t>A template opened in its own window next to the automatically computed bill of materials.</t>
-  </si>
-  <si>
-    <t>bom-template-window</t>
-  </si>
-  <si>
-    <t>editing/pile-dialog.png</t>
-  </si>
-  <si>
-    <t>Pile layout editor</t>
-  </si>
-  <si>
-    <t>The editor with several piles placed on the reference table, the drawing on one side and the coordinate table on the other.</t>
-  </si>
-  <si>
-    <t>Generate a layout, then switch the piles button on for the first time, or use Edit-Pile ▸ Define Pile Layout…</t>
-  </si>
-  <si>
-    <t>Mark the table's bottom-left corner as the origin and label the two axis directions.</t>
-  </si>
-  <si>
-    <t>/docs/editing/piles</t>
-  </si>
-  <si>
-    <t>The pile layout editor showing one reference table with piles placed on it and the coordinate table beside it.</t>
-  </si>
-  <si>
-    <t>pile-dialog</t>
-  </si>
-  <si>
-    <t>editing/piles-overlay.png</t>
-  </si>
-  <si>
-    <t>Piles across the plant</t>
-  </si>
-  <si>
-    <t>A zoomed plot view with the pile overlay on, showing the same pattern stamped on several neighbouring tables.</t>
-  </si>
-  <si>
-    <t>Define a pile pattern, then keep the piles button on and zoom into a block of tables.</t>
-  </si>
-  <si>
-    <t>A zoomed layout view with the pile pattern repeated on every table.</t>
-  </si>
-  <si>
-    <t>piles-overlay</t>
-  </si>
-  <si>
-    <t>editing/sketch-palette.png</t>
-  </si>
-  <si>
-    <t>The sketch tool palette</t>
-  </si>
-  <si>
-    <t>The full palette with every tool button label readable, including the snap, orthogonal, grid, undo and redo controls and the layer row.</t>
-  </si>
-  <si>
-    <t>Generate a layout, then switch Sketch Mode on. Capture the palette area of the panel; stitch if it does not fit.</t>
-  </si>
-  <si>
-    <t>Group the buttons and label the groups: select and edit, place, draw, annotate, trenches, navigate.</t>
-  </si>
-  <si>
-    <t>/docs/editing/sketch-mode</t>
-  </si>
-  <si>
-    <t>The sketch mode tool palette showing every drawing and editing tool.</t>
-  </si>
-  <si>
-    <t>sketch-palette</t>
-  </si>
-  <si>
-    <t>editing/sketch-selection.png</t>
-  </si>
-  <si>
-    <t>Selecting several tables</t>
-  </si>
-  <si>
-    <t>A zoomed plot view with a group of tables highlighted in the selection colour, ideally mid rubber-band so the selection rectangle is visible too.</t>
-  </si>
-  <si>
-    <t>In Sketch Mode with the move tool active, drag on empty space across a group of tables.</t>
-  </si>
-  <si>
-    <t>Outline the rubber-band rectangle.</t>
-  </si>
-  <si>
-    <t>Several tables highlighted as a selection after a rubber-band drag.</t>
-  </si>
-  <si>
-    <t>sketch-selection</t>
-  </si>
-  <si>
-    <t>energy/buttons.png</t>
-  </si>
-  <si>
-    <t>Energy controls</t>
-  </si>
-  <si>
-    <t>The energy button block: Calculate Energy, Show Energy Chart, the export button and its interval selector, plus the status line.</t>
-  </si>
-  <si>
-    <t>After a layout has been generated, so the buttons are enabled.</t>
-  </si>
-  <si>
-    <t>/docs/energy/overview</t>
-  </si>
-  <si>
-    <t>The Calculate Energy, Show Energy Chart and Export controls with the interval selector.</t>
-  </si>
-  <si>
-    <t>energy-buttons</t>
-  </si>
-  <si>
-    <t>energy/chart-daily.png</t>
-  </si>
-  <si>
-    <t>Daily energy and irradiance</t>
-  </si>
-  <si>
-    <t>The daily view with both charts drawn, the day slider visible, and the crosshair active so the readout strip shows values.</t>
-  </si>
-  <si>
-    <t>Calculate energy, click Show Energy Chart, and hover the pointer over the middle of the day.</t>
-  </si>
-  <si>
-    <t>Label the two charts and the day slider.</t>
-  </si>
-  <si>
-    <t>/docs/energy/timeseries</t>
-  </si>
-  <si>
-    <t>The daily chart with hourly energy bars above hourly irradiance bars, a day slider and a crosshair readout.</t>
-  </si>
-  <si>
-    <t>energy-chart-daily</t>
-  </si>
-  <si>
-    <t>energy/chart-monthly.png</t>
-  </si>
-  <si>
-    <t>Monthly energy and irradiance</t>
-  </si>
-  <si>
-    <t>The monthly view with all twelve months and the annual totals visible.</t>
-  </si>
-  <si>
-    <t>In the energy chart window, switch to the monthly view.</t>
-  </si>
-  <si>
-    <t>The monthly chart with twelve energy bars and twelve irradiance bars, plus the annual totals.</t>
-  </si>
-  <si>
-    <t>energy-chart-monthly</t>
-  </si>
-  <si>
-    <t>energy/degradation-pvalues.png</t>
-  </si>
-  <si>
-    <t>Degradation and probability settings</t>
-  </si>
-  <si>
-    <t>Both sections together: first-year and annual degradation, plant lifetime, combined uncertainty, and the three exceedance probability fields.</t>
-  </si>
-  <si>
-    <t>Nothing changed from defaults.</t>
-  </si>
-  <si>
-    <t>/docs/energy/lifetime-and-p-values</t>
-  </si>
-  <si>
-    <t>The degradation and probabilistic yield sections with their default values.</t>
-  </si>
-  <si>
-    <t>energy-degradation-pvalues</t>
-  </si>
-  <si>
     <t>energy/ghi-file-format.png</t>
   </si>
   <si>
@@ -281,7 +284,7 @@
     <t>The reminder with its full three-column table.</t>
   </si>
   <si>
-    <t>Select the hourly file option. The reminder appears immediately.</t>
+    <t>Select the hourly file option. The reminder appears immediately. Capture the reminder in the panel — not a weather file opened in a spreadsheet.</t>
   </si>
   <si>
     <t>/docs/energy/weather</t>
@@ -320,16 +323,16 @@
     <t>Performance ratio breakdown</t>
   </si>
   <si>
-    <t>The whole performance ratio section at its defaults, including the module temperature readout row, the shading auto-compute checkbox and the ground clearance row.</t>
-  </si>
-  <si>
-    <t>Nothing changed from defaults, in a String Inverter mode so the cable row labels read that way.</t>
+    <t>The performance ratio section at its defaults, from the inverter efficiency row down to the shading row, including the module temperature readout beneath the temperature loss.</t>
+  </si>
+  <si>
+    <t>Nothing changed from defaults, in a Central Inverter mode, so the two cable rows read MMS → SMB and SMB → Central Inv.</t>
   </si>
   <si>
     <t>/docs/energy/losses</t>
   </si>
   <si>
-    <t>The performance ratio breakdown listing every loss component with its percentage.</t>
+    <t>The performance ratio breakdown in the input panel, listing inverter efficiency, the two cable losses, soiling, temperature with its module temperature readout, mismatch and shading.</t>
   </si>
   <si>
     <t>energy-losses-group</t>
@@ -341,19 +344,16 @@
     <t>Shadow view</t>
   </si>
   <si>
-    <t>The shadow view with three rows drawn, a shadow clearly falling on the row behind, and both sliders visible with their current day and hour.</t>
-  </si>
-  <si>
-    <t>Generate a layout, click Shadow View, then move the day slider to midwinter and the hour slider to early morning so a shadow is actually cast.</t>
-  </si>
-  <si>
-    <t>Label the shaded part of the rear row and both sliders.</t>
+    <t>The between-rows side view: three rows drawn, the geometry line reporting row pitch, ground coverage ratio and tilt, the tilt / pitch / lower-edge inputs, and the readout line reporting the day, the hour, the sun elevation, the profile angle and whether the rear row is shaded.</t>
+  </si>
+  <si>
+    <t>Generate a layout and click Shadow View, then move the day and hour sliders to the sun position you want to show — the readout line reports it.</t>
   </si>
   <si>
     <t>/docs/energy/shading</t>
   </si>
   <si>
-    <t>A side-view cross-section of three rows showing where the front row's shadow falls on the row behind, with day and time sliders.</t>
+    <t>A side-view cross-section of three rows with the sun's rays drawn and the front row's shadow reaching the ground short of the row behind, above a readout of the day, hour, sun elevation and shading state.</t>
   </si>
   <si>
     <t>shadow-view</t>
@@ -368,7 +368,7 @@
     <t>The summary table scrolled to its right-hand end so the three probability columns, the capacity factor and the lifetime energy column are all readable.</t>
   </si>
   <si>
-    <t>Generate a layout, calculate energy, then scroll the summary table right — or use the maximised window.</t>
+    <t>Generate a layout, calculate energy, then scroll the summary table right — or use the maximised window. The three probability columns must be in frame; the monthly table below the summary is a different image.</t>
   </si>
   <si>
     <t>Label the three probability columns.</t>
@@ -389,7 +389,7 @@
     <t>The mounting type, wind speed and ambient temperature fields, the temperature loss row with the computed module temperature next to it, and the formula trace line.</t>
   </si>
   <si>
-    <t>Load a module file so the temperature model has a coefficient to work with, and set an irradiance value.</t>
+    <t>Load a module file so the temperature model has a coefficient to work with, and set an irradiance value — without one the module temperature reads a dash and there is no trace line to show.</t>
   </si>
   <si>
     <t>Outline the formula trace line.</t>
@@ -431,7 +431,7 @@
     <t>/docs/exports/pdf-report</t>
   </si>
   <si>
-    <t>The export buttons for the report, the pile report, the mapping file and the drawing file.</t>
+    <t>The export block with the Export KMZ, Export DXF and Export PDF (Layout + Summary) buttons.</t>
   </si>
   <si>
     <t>export-buttons</t>
@@ -446,7 +446,7 @@
     <t>A CAD program with the exported drawing open and the layer panel visible, so the layer names can be read against the drawing.</t>
   </si>
   <si>
-    <t>Export the drawing file and open it in AutoCAD or BricsCAD. Show the layer manager.</t>
+    <t>Export the drawing file and open it in AutoCAD or BricsCAD, and show the layer manager. The frame is the CAD program, not the save window.</t>
   </si>
   <si>
     <t>Outline the layer list.</t>
@@ -470,7 +470,7 @@
     <t>Google Earth with the exported file open, the Places tree expanded to show the per-plant folders and the summary folder, and the layout drawn over the imagery.</t>
   </si>
   <si>
-    <t>Export the mapping file, then open it in Google Earth Pro and expand the tree.</t>
+    <t>Export the mapping file, then open it in Google Earth Pro and expand the tree. The frame is Google Earth, not the save window.</t>
   </si>
   <si>
     <t>Label the per-plant folder and the summary placemark.</t>
@@ -647,7 +647,7 @@
     <t>Google Earth with the Places panel visible, showing one plant boundary polygon that contains a water polygon, an obstruction polygon and a transmission LineString — with the feature names readable in the panel so the naming rules are obvious.</t>
   </si>
   <si>
-    <t>Open a prepared demonstration file in Google Earth Pro. Expand the Places tree so every feature name shows.</t>
+    <t>Open a prepared demonstration file in Google Earth Pro — not the application's own file chooser. Expand the Places tree so every feature name shows.</t>
   </si>
   <si>
     <t>Label each feature with its type: boundary, water, obstruction, transmission line.</t>
@@ -962,22 +962,19 @@
     <t>layout/cables-dc-ac.png</t>
   </si>
   <si>
-    <t>String and feeder cable routing</t>
-  </si>
-  <si>
-    <t>A zoomed view with both cable types switched on, close enough that the right-angled routing and the inverter positions are clear.</t>
-  </si>
-  <si>
-    <t>Generate with cable calculation on, then switch both cable displays on and zoom into one block.</t>
-  </si>
-  <si>
-    <t>Label one string cable, one feeder cable and one inverter.</t>
+    <t>String and collection cable routing</t>
+  </si>
+  <si>
+    <t>The plot with both cable displays switched on, close enough that the right-angled routing and the collection points are clear. Captured in Central Inverter mode, so both runs are direct current — the strings to the monitoring boxes, the trunks on to the control rooms.</t>
+  </si>
+  <si>
+    <t>Generate with cable calculation on, then switch both cable displays on.</t>
   </si>
   <si>
     <t>/docs/layout/cables</t>
   </si>
   <si>
-    <t>A layout with direct-current string cables and alternating-current feeder cables both drawn.</t>
+    <t>A layout with the string cables from the tables and the collection cables on to the control rooms both drawn, every run at right angles.</t>
   </si>
   <si>
     <t>layout-cables-dc-ac</t>
@@ -989,7 +986,7 @@
     <t>Medium-voltage cables sharing a trunk</t>
   </si>
   <si>
-    <t>The plot with the medium-voltage display on, showing several control rooms' cables merging into a shared trunk rather than running in parallel.</t>
+    <t>The plot with the medium-voltage display on, showing the control rooms' cables joining a shared run rather than travelling in parallel.</t>
   </si>
   <si>
     <t>Generate with cable calculation on, place the main control room, then switch the medium-voltage display on.</t>
@@ -998,7 +995,7 @@
     <t>Mark a junction where two routes merge.</t>
   </si>
   <si>
-    <t>Medium-voltage cables running from several control rooms and merging into a shared trunk toward the main control room.</t>
+    <t>Medium-voltage cables running from the inverter control rooms and joining on the way to the main control room.</t>
   </si>
   <si>
     <t>layout-cables-mv</t>
@@ -1271,22 +1268,22 @@
     <t>licence/no-licence.png</t>
   </si>
   <si>
-    <t>License window before activation</t>
-  </si>
-  <si>
-    <t>Help ▸ License / Subscription… on a machine with no licence installed: the status banner, the Device ID box with its Copy button, and the Load License File… button.</t>
-  </si>
-  <si>
-    <t>Launch the app on a machine that has never had a licence installed, then open Help ▸ License / Subscription…</t>
-  </si>
-  <si>
-    <t>Number the Device ID field 1 and the Load License File… button 2. Blur the Device ID value itself.</t>
+    <t>License window with no active access</t>
+  </si>
+  <si>
+    <t>Help ▸ License / Subscription… on a device with no active access: the ✗ No access status headline, the Your Device ID field with its Copy button, and the Get Free Access, Contact Us, Refresh and Close buttons.</t>
+  </si>
+  <si>
+    <t>Launch the app on a device with no active access, then open Help ▸ License / Subscription…</t>
+  </si>
+  <si>
+    <t>Number the Device ID field 1 and the Get Free Access button 2. Blur the Device ID value itself.</t>
   </si>
   <si>
     <t>/docs/licence/activate</t>
   </si>
   <si>
-    <t>The License and Subscription window showing no licence found, with the Device ID field and a Copy button.</t>
+    <t>The License / Subscription window on a device with no active access, showing the Device ID field, its Copy button, and the Get Free Access button.</t>
   </si>
   <si>
     <t>licence-no-licence</t>
@@ -1295,19 +1292,19 @@
     <t>licence/valid.png</t>
   </si>
   <si>
-    <t>License window after activation</t>
-  </si>
-  <si>
-    <t>The same window after a valid licence has been loaded — the status banner reports the licence as valid and shows the expiry date.</t>
-  </si>
-  <si>
-    <t>Load a valid license.lic through Load License File…, then reopen the window.</t>
-  </si>
-  <si>
-    <t>Outline the status banner. Blur the email address and Device ID.</t>
-  </si>
-  <si>
-    <t>The License and Subscription window showing a valid licence with its expiry date.</t>
+    <t>License window with active access</t>
+  </si>
+  <si>
+    <t>The same window on a device with active access — the ✓ Active headline and the 'You have access until &lt;date&gt;.' line, with the Access Details, Refresh and Close buttons.</t>
+  </si>
+  <si>
+    <t>On a device with active access, open Help ▸ License / Subscription…</t>
+  </si>
+  <si>
+    <t>Outline the status banner. Blur the Device ID.</t>
+  </si>
+  <si>
+    <t>The License / Subscription window on a device with active access, showing the Active headline and the date access runs until.</t>
   </si>
   <si>
     <t>licence-valid</t>
@@ -1364,15 +1361,12 @@
     <t>Cleaning robot sizing</t>
   </si>
   <si>
-    <t>The window with the battery and bridge inputs at the top, both gap lists populated — gaps blocked by equipment and gaps in open ground — and the resulting fleet size.</t>
+    <t>The window with the robot inputs at the top, the list of gaps blocked by equipment with their tick boxes, and the result line reporting the fleet size, the bridges and the gaps in open ground.</t>
   </si>
   <si>
     <t>Generate a layout on a site with arresters, control rooms or obstructions so there are wide gaps to list, then click the robotic cleaning button.</t>
   </si>
   <si>
-    <t>Label the two gap groups and the fleet result.</t>
-  </si>
-  <si>
     <t>/docs/simulation/robotic-cleaning</t>
   </si>
   <si>
@@ -1613,6 +1607,78 @@
     <t>energy-ghi-file-loaded</t>
   </si>
   <si>
+    <t>energy/monthly-table.png</t>
+  </si>
+  <si>
+    <t>The monthly table</t>
+  </si>
+  <si>
+    <t>The month-by-month table below the summary, with every column header readable: GHI, H_i, T_amb, T_cell, Y_r, Y_f, PR, Energy and CUF.</t>
+  </si>
+  <si>
+    <t>Generate a layout and click Calculate Energy, then read the table below the summary.</t>
+  </si>
+  <si>
+    <t>The monthly energy breakdown below the plot, one row per month, with horizontal and in-plane irradiation, ambient and cell temperature, reference and final yield, performance ratio, energy and capacity factor.</t>
+  </si>
+  <si>
+    <t>energy-monthly-table</t>
+  </si>
+  <si>
+    <t>energy/pr-breakdown-report.png</t>
+  </si>
+  <si>
+    <t>The breakdown as the report prints it</t>
+  </si>
+  <si>
+    <t>The performance ratio breakdown on the report's energy page — every component with its input percentage and its factor, ending in the OVERALL PR row.</t>
+  </si>
+  <si>
+    <t>Calculate energy, export the report, then open its energy page.</t>
+  </si>
+  <si>
+    <t>The report's performance ratio breakdown table: one row per loss component with its input percentage and the factor it contributes, and the overall performance ratio on the last row.</t>
+  </si>
+  <si>
+    <t>energy-pr-breakdown-report</t>
+  </si>
+  <si>
+    <t>exports/dxf-save-dialog.png</t>
+  </si>
+  <si>
+    <t>Saving the drawing file</t>
+  </si>
+  <si>
+    <t>The save window that opens on Export DXF: the folder being written to, the file name field and the DXF file type row.</t>
+  </si>
+  <si>
+    <t>Generate a layout, then click Export DXF.</t>
+  </si>
+  <si>
+    <t>The Save DXF window, with an empty file name field and the file type set to DXF files.</t>
+  </si>
+  <si>
+    <t>export-dxf-save-dialog</t>
+  </si>
+  <si>
+    <t>exports/kmz-save-dialog.png</t>
+  </si>
+  <si>
+    <t>Saving the mapping file</t>
+  </si>
+  <si>
+    <t>The save window that opens on Export KMZ: the folder being written to, the file name field and the KMZ file type row.</t>
+  </si>
+  <si>
+    <t>Generate a layout, then click Export KMZ.</t>
+  </si>
+  <si>
+    <t>The Save KMZ window, with an empty file name field and the file type set to KMZ files.</t>
+  </si>
+  <si>
+    <t>export-kmz-save-dialog</t>
+  </si>
+  <si>
     <t>exports/kmz-summary-placemark.png</t>
   </si>
   <si>
@@ -1685,6 +1751,24 @@
     <t>pdf-page-sld</t>
   </si>
   <si>
+    <t>inputs/boundary-file-picker.png</t>
+  </si>
+  <si>
+    <t>Choosing a boundary file</t>
+  </si>
+  <si>
+    <t>The file chooser opened by Browse…, with the boundary file type row readable, sitting over the input panel.</t>
+  </si>
+  <si>
+    <t>Click Browse… in the Input KMZ File group.</t>
+  </si>
+  <si>
+    <t>The Select boundary file window open over the input panel, with the file type row listing the boundary extensions it accepts.</t>
+  </si>
+  <si>
+    <t>boundary-file-picker</t>
+  </si>
+  <si>
     <t>inputs/boundary-validation.png</t>
   </si>
   <si>
@@ -2000,19 +2084,19 @@
     <t>licence/blocked-generate.png</t>
   </si>
   <si>
-    <t>Generate blocked without a licence</t>
-  </si>
-  <si>
-    <t>The message the app shows when Generate Layout is clicked and no valid licence is present.</t>
-  </si>
-  <si>
-    <t>With no licence installed, load a boundary file and click Generate Layout.</t>
+    <t>Generate blocked without active access</t>
+  </si>
+  <si>
+    <t>The Subscription Required dialog the app shows when Generate Layout is clicked and this device has no active access.</t>
+  </si>
+  <si>
+    <t>With no active access, load a boundary file and click Generate Layout.</t>
   </si>
   <si>
     <t>/docs/licence/overview</t>
   </si>
   <si>
-    <t>The message shown when Generate Layout is clicked without a valid licence.</t>
+    <t>The Subscription Required message shown when Generate Layout is clicked without active access.</t>
   </si>
   <si>
     <t>licence-blocked-generate</t>
@@ -2150,7 +2234,7 @@
     <t>The editor with a traced symbol visible and the three editing tools.</t>
   </si>
   <si>
-    <t>In diagram mode, import an image symbol. The editor opens automatically.</t>
+    <t>In diagram mode, import an image symbol — the editor opens on its own. The frame is that editor window, not diagram mode itself.</t>
   </si>
   <si>
     <t>The symbol editor showing strokes traced from an image, with pen, erase and clear tools.</t>
@@ -2334,7 +2418,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -2348,11 +2432,15 @@
     </font>
     <font>
       <b/>
-      <color rgb="FFB4530A"/>
+      <color rgb="FF1A6E3C"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Consolas"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFB4530A"/>
     </font>
   </fonts>
   <fills count="3">
@@ -2380,7 +2468,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2392,6 +2480,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2734,7 +2825,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K105"/>
+  <dimension ref="A1:K110"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -3142,32 +3233,32 @@
       <c r="B12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>12</v>
+      <c r="C12" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3181,28 +3272,28 @@
         <v>12</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3216,28 +3307,28 @@
         <v>12</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3251,19 +3342,19 @@
         <v>12</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>112</v>
@@ -3282,8 +3373,8 @@
       <c r="B16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>12</v>
+      <c r="C16" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>115</v>
@@ -3317,8 +3408,8 @@
       <c r="B17" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>12</v>
+      <c r="C17" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>122</v>
@@ -3352,8 +3443,8 @@
       <c r="B18" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>12</v>
+      <c r="C18" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>130</v>
@@ -3371,7 +3462,7 @@
         <v>17</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>133</v>
@@ -3422,8 +3513,8 @@
       <c r="B20" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>12</v>
+      <c r="C20" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>141</v>
@@ -3457,8 +3548,8 @@
       <c r="B21" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>12</v>
+      <c r="C21" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>149</v>
@@ -3562,8 +3653,8 @@
       <c r="B24" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>12</v>
+      <c r="C24" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>171</v>
@@ -3597,8 +3688,8 @@
       <c r="B25" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>12</v>
+      <c r="C25" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>179</v>
@@ -3632,8 +3723,8 @@
       <c r="B26" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>12</v>
+      <c r="C26" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>186</v>
@@ -3667,8 +3758,8 @@
       <c r="B27" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>12</v>
+      <c r="C27" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>194</v>
@@ -3702,8 +3793,8 @@
       <c r="B28" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>12</v>
+      <c r="C28" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>202</v>
@@ -3737,8 +3828,8 @@
       <c r="B29" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>12</v>
+      <c r="C29" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>208</v>
@@ -3772,8 +3863,8 @@
       <c r="B30" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>12</v>
+      <c r="C30" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>216</v>
@@ -3807,8 +3898,8 @@
       <c r="B31" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>12</v>
+      <c r="C31" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>223</v>
@@ -3842,8 +3933,8 @@
       <c r="B32" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>12</v>
+      <c r="C32" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>230</v>
@@ -3877,8 +3968,8 @@
       <c r="B33" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>12</v>
+      <c r="C33" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>237</v>
@@ -3912,8 +4003,8 @@
       <c r="B34" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>12</v>
+      <c r="C34" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>243</v>
@@ -3947,8 +4038,8 @@
       <c r="B35" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>12</v>
+      <c r="C35" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>251</v>
@@ -3982,8 +4073,8 @@
       <c r="B36" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>12</v>
+      <c r="C36" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>257</v>
@@ -4017,8 +4108,8 @@
       <c r="B37" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>12</v>
+      <c r="C37" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>265</v>
@@ -4052,8 +4143,8 @@
       <c r="B38" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>12</v>
+      <c r="C38" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>271</v>
@@ -4087,8 +4178,8 @@
       <c r="B39" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>12</v>
+      <c r="C39" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>278</v>
@@ -4122,8 +4213,8 @@
       <c r="B40" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>12</v>
+      <c r="C40" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>285</v>
@@ -4157,8 +4248,8 @@
       <c r="B41" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>12</v>
+      <c r="C41" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>291</v>
@@ -4192,8 +4283,8 @@
       <c r="B42" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>12</v>
+      <c r="C42" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>299</v>
@@ -4278,16 +4369,16 @@
         <v>318</v>
       </c>
       <c r="H44" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I44" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="I44" s="2" t="s">
+      <c r="J44" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="J44" s="2" t="s">
+      <c r="K44" s="4" t="s">
         <v>321</v>
-      </c>
-      <c r="K44" s="4" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="45" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4301,28 +4392,28 @@
         <v>12</v>
       </c>
       <c r="D45" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="F45" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="F45" s="2" t="s">
+      <c r="G45" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="G45" s="2" t="s">
+      <c r="H45" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="H45" s="2" t="s">
+      <c r="I45" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="J45" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="I45" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="J45" s="2" t="s">
+      <c r="K45" s="4" t="s">
         <v>328</v>
-      </c>
-      <c r="K45" s="4" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="46" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4332,32 +4423,32 @@
       <c r="B46" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>12</v>
+      <c r="C46" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D46" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="E46" s="2" t="s">
+      <c r="F46" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="F46" s="2" t="s">
+      <c r="G46" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="G46" s="2" t="s">
+      <c r="H46" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="H46" s="2" t="s">
+      <c r="I46" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="I46" s="2" t="s">
+      <c r="J46" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="J46" s="2" t="s">
+      <c r="K46" s="4" t="s">
         <v>336</v>
-      </c>
-      <c r="K46" s="4" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="47" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4367,32 +4458,32 @@
       <c r="B47" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>12</v>
+      <c r="C47" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D47" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="F47" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="F47" s="2" t="s">
+      <c r="G47" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="G47" s="2" t="s">
+      <c r="H47" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="H47" s="2" t="s">
+      <c r="I47" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="J47" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="I47" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="J47" s="2" t="s">
+      <c r="K47" s="4" t="s">
         <v>343</v>
-      </c>
-      <c r="K47" s="4" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="48" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4402,32 +4493,32 @@
       <c r="B48" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>12</v>
+      <c r="C48" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D48" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="F48" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="F48" s="2" t="s">
+      <c r="G48" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="G48" s="2" t="s">
+      <c r="H48" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="H48" s="2" t="s">
+      <c r="I48" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="I48" s="2" t="s">
+      <c r="J48" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="J48" s="2" t="s">
+      <c r="K48" s="4" t="s">
         <v>351</v>
-      </c>
-      <c r="K48" s="4" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="49" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4437,32 +4528,32 @@
       <c r="B49" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C49" s="3" t="s">
-        <v>12</v>
+      <c r="C49" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D49" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="E49" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="E49" s="2" t="s">
+      <c r="F49" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="F49" s="2" t="s">
+      <c r="G49" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="G49" s="2" t="s">
+      <c r="H49" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="H49" s="2" t="s">
+      <c r="I49" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="I49" s="2" t="s">
+      <c r="J49" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="J49" s="2" t="s">
+      <c r="K49" s="4" t="s">
         <v>359</v>
-      </c>
-      <c r="K49" s="4" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="50" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4472,32 +4563,32 @@
       <c r="B50" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C50" s="3" t="s">
-        <v>12</v>
+      <c r="C50" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D50" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="E50" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="F50" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="F50" s="2" t="s">
+      <c r="G50" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="G50" s="2" t="s">
+      <c r="H50" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="H50" s="2" t="s">
+      <c r="I50" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="I50" s="2" t="s">
+      <c r="J50" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="J50" s="2" t="s">
+      <c r="K50" s="4" t="s">
         <v>367</v>
-      </c>
-      <c r="K50" s="4" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="51" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4507,32 +4598,32 @@
       <c r="B51" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C51" s="3" t="s">
-        <v>12</v>
+      <c r="C51" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D51" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="E51" s="2" t="s">
+      <c r="F51" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="F51" s="2" t="s">
+      <c r="G51" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="G51" s="2" t="s">
+      <c r="H51" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="H51" s="2" t="s">
+      <c r="I51" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="I51" s="2" t="s">
+      <c r="J51" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="J51" s="2" t="s">
+      <c r="K51" s="4" t="s">
         <v>375</v>
-      </c>
-      <c r="K51" s="4" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="52" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4542,32 +4633,32 @@
       <c r="B52" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>12</v>
+      <c r="C52" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D52" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="E52" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="E52" s="2" t="s">
+      <c r="F52" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="F52" s="2" t="s">
+      <c r="G52" s="2" t="s">
         <v>379</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>380</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I52" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="J52" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="J52" s="2" t="s">
+      <c r="K52" s="4" t="s">
         <v>382</v>
-      </c>
-      <c r="K52" s="4" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="53" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4577,32 +4668,32 @@
       <c r="B53" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C53" s="3" t="s">
-        <v>12</v>
+      <c r="C53" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D53" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="E53" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="E53" s="2" t="s">
+      <c r="F53" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="F53" s="2" t="s">
+      <c r="G53" s="2" t="s">
         <v>386</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>387</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J53" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="K53" s="4" t="s">
         <v>388</v>
-      </c>
-      <c r="K53" s="4" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="54" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4612,32 +4703,32 @@
       <c r="B54" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C54" s="3" t="s">
-        <v>12</v>
+      <c r="C54" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D54" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="E54" s="2" t="s">
+      <c r="F54" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="F54" s="2" t="s">
+      <c r="G54" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="G54" s="2" t="s">
+      <c r="H54" s="2" t="s">
         <v>393</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>394</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>288</v>
       </c>
       <c r="J54" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="K54" s="4" t="s">
         <v>395</v>
-      </c>
-      <c r="K54" s="4" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="55" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4647,32 +4738,32 @@
       <c r="B55" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C55" s="3" t="s">
-        <v>12</v>
+      <c r="C55" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D55" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="E55" s="2" t="s">
+      <c r="F55" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="F55" s="2" t="s">
+      <c r="G55" s="2" t="s">
         <v>399</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>400</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I55" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="J55" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="J55" s="2" t="s">
+      <c r="K55" s="4" t="s">
         <v>402</v>
-      </c>
-      <c r="K55" s="4" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="56" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4682,32 +4773,32 @@
       <c r="B56" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>12</v>
+      <c r="C56" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D56" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="E56" s="2" t="s">
+      <c r="F56" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="F56" s="2" t="s">
+      <c r="G56" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="G56" s="2" t="s">
+      <c r="H56" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="H56" s="2" t="s">
+      <c r="I56" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="I56" s="2" t="s">
+      <c r="J56" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="J56" s="2" t="s">
+      <c r="K56" s="4" t="s">
         <v>410</v>
-      </c>
-      <c r="K56" s="4" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="57" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4717,32 +4808,32 @@
       <c r="B57" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C57" s="3" t="s">
-        <v>12</v>
+      <c r="C57" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D57" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="E57" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="E57" s="2" t="s">
+      <c r="F57" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="F57" s="2" t="s">
+      <c r="G57" s="2" t="s">
         <v>414</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>415</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="J57" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="K57" s="4" t="s">
         <v>416</v>
-      </c>
-      <c r="K57" s="4" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="58" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4752,32 +4843,32 @@
       <c r="B58" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C58" s="3" t="s">
-        <v>12</v>
+      <c r="C58" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D58" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="E58" s="2" t="s">
+      <c r="F58" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="F58" s="2" t="s">
+      <c r="G58" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="G58" s="2" t="s">
+      <c r="H58" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="H58" s="2" t="s">
+      <c r="I58" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="I58" s="2" t="s">
+      <c r="J58" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="J58" s="2" t="s">
+      <c r="K58" s="4" t="s">
         <v>424</v>
-      </c>
-      <c r="K58" s="4" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="59" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4787,32 +4878,32 @@
       <c r="B59" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C59" s="3" t="s">
-        <v>12</v>
+      <c r="C59" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D59" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="E59" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="E59" s="2" t="s">
+      <c r="F59" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="F59" s="2" t="s">
+      <c r="G59" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="G59" s="2" t="s">
+      <c r="H59" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="H59" s="2" t="s">
+      <c r="I59" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="J59" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="I59" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="J59" s="2" t="s">
+      <c r="K59" s="4" t="s">
         <v>431</v>
-      </c>
-      <c r="K59" s="4" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="60" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4822,32 +4913,32 @@
       <c r="B60" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C60" s="3" t="s">
-        <v>12</v>
+      <c r="C60" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D60" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="E60" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="F60" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="F60" s="2" t="s">
+      <c r="G60" s="2" t="s">
         <v>435</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>436</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I60" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="J60" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="J60" s="2" t="s">
+      <c r="K60" s="4" t="s">
         <v>438</v>
-      </c>
-      <c r="K60" s="4" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="61" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4857,32 +4948,32 @@
       <c r="B61" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C61" s="3" t="s">
-        <v>12</v>
+      <c r="C61" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D61" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="E61" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="E61" s="2" t="s">
+      <c r="F61" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="F61" s="2" t="s">
+      <c r="G61" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="G61" s="2" t="s">
+      <c r="H61" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="H61" s="2" t="s">
+      <c r="I61" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="I61" s="2" t="s">
+      <c r="J61" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J61" s="2" t="s">
+      <c r="K61" s="4" t="s">
         <v>446</v>
-      </c>
-      <c r="K61" s="4" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="62" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4896,28 +4987,28 @@
         <v>12</v>
       </c>
       <c r="D62" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="E62" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="E62" s="2" t="s">
+      <c r="F62" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="F62" s="2" t="s">
+      <c r="G62" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="G62" s="2" t="s">
+      <c r="H62" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I62" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="H62" s="2" t="s">
+      <c r="J62" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="I62" s="2" t="s">
+      <c r="K62" s="4" t="s">
         <v>453</v>
-      </c>
-      <c r="J62" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="K62" s="4" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="63" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4931,28 +5022,28 @@
         <v>12</v>
       </c>
       <c r="D63" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="F63" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="E63" s="2" t="s">
+      <c r="G63" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="F63" s="2" t="s">
+      <c r="H63" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="G63" s="2" t="s">
+      <c r="I63" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="H63" s="2" t="s">
+      <c r="J63" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="I63" s="2" t="s">
+      <c r="K63" s="4" t="s">
         <v>461</v>
-      </c>
-      <c r="J63" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="K63" s="4" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="64" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4966,28 +5057,28 @@
         <v>12</v>
       </c>
       <c r="D64" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="F64" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="E64" s="2" t="s">
+      <c r="G64" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="F64" s="2" t="s">
+      <c r="H64" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="G64" s="2" t="s">
+      <c r="I64" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="H64" s="2" t="s">
+      <c r="J64" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="I64" s="2" t="s">
+      <c r="K64" s="4" t="s">
         <v>469</v>
-      </c>
-      <c r="J64" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="K64" s="4" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="65" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5001,28 +5092,28 @@
         <v>12</v>
       </c>
       <c r="D65" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="F65" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="E65" s="2" t="s">
+      <c r="G65" s="2" t="s">
         <v>473</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>475</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I65" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="K65" s="4" t="s">
         <v>476</v>
-      </c>
-      <c r="J65" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="K65" s="4" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="66" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5032,32 +5123,32 @@
       <c r="B66" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C66" s="3" t="s">
-        <v>12</v>
+      <c r="C66" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D66" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="F66" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="E66" s="2" t="s">
+      <c r="G66" s="2" t="s">
         <v>480</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>482</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="K66" s="4" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="67" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5067,32 +5158,32 @@
       <c r="B67" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C67" s="3" t="s">
-        <v>12</v>
+      <c r="C67" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D67" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="F67" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="E67" s="2" t="s">
+      <c r="G67" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="F67" s="2" t="s">
+      <c r="H67" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="G67" s="2" t="s">
+      <c r="I67" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="H67" s="2" t="s">
+      <c r="J67" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="I67" s="2" t="s">
+      <c r="K67" s="4" t="s">
         <v>490</v>
-      </c>
-      <c r="J67" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="K67" s="4" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="68" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5100,34 +5191,34 @@
         <v>67</v>
       </c>
       <c r="B68" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="E68" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="C68" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D68" s="4" t="s">
+      <c r="F68" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="E68" s="2" t="s">
+      <c r="G68" s="2" t="s">
         <v>495</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="G68" s="2" t="s">
-        <v>497</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I68" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="K68" s="4" t="s">
         <v>498</v>
-      </c>
-      <c r="J68" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="K68" s="4" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="69" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5135,34 +5226,34 @@
         <v>68</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>12</v>
+        <v>491</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D69" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="F69" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="E69" s="2" t="s">
+      <c r="G69" s="2" t="s">
         <v>502</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>504</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="70" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5170,34 +5261,34 @@
         <v>69</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>12</v>
+        <v>491</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D70" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="F70" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="E70" s="2" t="s">
+      <c r="G70" s="2" t="s">
         <v>508</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>510</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="K70" s="4" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="71" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5205,34 +5296,34 @@
         <v>70</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>12</v>
+        <v>491</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D71" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="F71" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="E71" s="2" t="s">
+      <c r="G71" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="F71" s="2" t="s">
+      <c r="H71" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="G71" s="2" t="s">
+      <c r="I71" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="J71" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="H71" s="2" t="s">
+      <c r="K71" s="4" t="s">
         <v>517</v>
-      </c>
-      <c r="I71" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="J71" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="K71" s="4" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="72" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5240,19 +5331,19 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>12</v>
+        <v>491</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D72" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="F72" s="2" t="s">
         <v>520</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>522</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>82</v>
@@ -5261,13 +5352,13 @@
         <v>17</v>
       </c>
       <c r="I72" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="K72" s="4" t="s">
         <v>523</v>
-      </c>
-      <c r="J72" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="K72" s="4" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="73" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5275,34 +5366,34 @@
         <v>72</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>12</v>
+        <v>491</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D73" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="F73" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="E73" s="2" t="s">
+      <c r="G73" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="F73" s="2" t="s">
+      <c r="H73" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="G73" s="2" t="s">
+      <c r="I73" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="J73" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="H73" s="2" t="s">
+      <c r="K73" s="4" t="s">
         <v>530</v>
-      </c>
-      <c r="I73" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="J73" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="K73" s="4" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="74" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5310,34 +5401,34 @@
         <v>73</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D74" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="F74" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="E74" s="2" t="s">
+      <c r="G74" s="2" t="s">
         <v>534</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>536</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>154</v>
+        <v>62</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="K74" s="4" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="75" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5345,34 +5436,34 @@
         <v>74</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D75" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="F75" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="E75" s="2" t="s">
+      <c r="G75" s="2" t="s">
         <v>540</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="G75" s="2" t="s">
-        <v>542</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="76" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5380,34 +5471,34 @@
         <v>75</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D76" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="F76" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="E76" s="2" t="s">
+      <c r="G76" s="2" t="s">
         <v>546</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>548</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="77" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5415,34 +5506,34 @@
         <v>76</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D77" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="F77" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="E77" s="2" t="s">
+      <c r="G77" s="2" t="s">
         <v>552</v>
-      </c>
-      <c r="F77" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="G77" s="2" t="s">
-        <v>554</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="78" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5450,34 +5541,34 @@
         <v>77</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>12</v>
+        <v>491</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D78" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="F78" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="E78" s="2" t="s">
+      <c r="G78" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="F78" s="2" t="s">
+      <c r="H78" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="J78" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="G78" s="2" t="s">
+      <c r="K78" s="4" t="s">
         <v>560</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="I78" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="J78" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="K78" s="4" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="79" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5485,34 +5576,34 @@
         <v>78</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>12</v>
+        <v>491</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D79" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="G79" s="2" t="s">
         <v>564</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="G79" s="2" t="s">
-        <v>567</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>199</v>
+        <v>138</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="80" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5520,34 +5611,34 @@
         <v>79</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>12</v>
+        <v>491</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D80" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="G80" s="2" t="s">
         <v>570</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="F80" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="G80" s="2" t="s">
-        <v>573</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>213</v>
+        <v>138</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
     </row>
     <row r="81" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5555,34 +5646,34 @@
         <v>80</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>12</v>
+        <v>491</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D81" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="G81" s="2" t="s">
         <v>576</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="F81" s="2" t="s">
-        <v>578</v>
-      </c>
-      <c r="G81" s="2" t="s">
-        <v>579</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>199</v>
+        <v>138</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="82" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5590,34 +5681,34 @@
         <v>81</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D82" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="G82" s="2" t="s">
         <v>582</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="G82" s="2" t="s">
-        <v>585</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
     </row>
     <row r="83" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5625,34 +5716,34 @@
         <v>82</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>12</v>
+        <v>491</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D83" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="G83" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="E83" s="2" t="s">
+      <c r="H83" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="F83" s="2" t="s">
+      <c r="I83" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="J83" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="G83" s="2" t="s">
+      <c r="K83" s="4" t="s">
         <v>591</v>
-      </c>
-      <c r="H83" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I83" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="J83" s="2" t="s">
-        <v>592</v>
-      </c>
-      <c r="K83" s="4" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="84" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5660,34 +5751,34 @@
         <v>83</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>12</v>
+        <v>491</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D84" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="F84" s="2" t="s">
         <v>594</v>
       </c>
-      <c r="E84" s="2" t="s">
+      <c r="G84" s="2" t="s">
         <v>595</v>
-      </c>
-      <c r="F84" s="2" t="s">
-        <v>596</v>
-      </c>
-      <c r="G84" s="2" t="s">
-        <v>597</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>304</v>
+        <v>199</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="K84" s="4" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="85" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5695,34 +5786,34 @@
         <v>84</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>12</v>
+        <v>491</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D85" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="F85" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="E85" s="2" t="s">
+      <c r="G85" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="F85" s="2" t="s">
+      <c r="H85" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="J85" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="G85" s="2" t="s">
+      <c r="K85" s="4" t="s">
         <v>603</v>
-      </c>
-      <c r="H85" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="I85" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="J85" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="K85" s="4" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="86" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5730,34 +5821,34 @@
         <v>85</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>12</v>
+        <v>491</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D86" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="J86" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="E86" s="2" t="s">
+      <c r="K86" s="4" t="s">
         <v>609</v>
-      </c>
-      <c r="F86" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="G86" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="H86" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="I86" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="J86" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="K86" s="4" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="87" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5765,34 +5856,34 @@
         <v>86</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>12</v>
+        <v>491</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D87" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="J87" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="K87" s="4" t="s">
         <v>615</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="F87" s="2" t="s">
-        <v>617</v>
-      </c>
-      <c r="G87" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="H87" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="I87" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="J87" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="K87" s="4" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="88" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5800,34 +5891,34 @@
         <v>87</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>12</v>
+        <v>491</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>626</v>
+        <v>17</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>350</v>
+        <v>220</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="K88" s="4" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
     </row>
     <row r="89" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5835,34 +5926,34 @@
         <v>88</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>12</v>
+        <v>491</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>631</v>
+        <v>624</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>374</v>
+        <v>304</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
       <c r="K89" s="4" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
     </row>
     <row r="90" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5870,34 +5961,34 @@
         <v>89</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>12</v>
+        <v>491</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D90" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="J90" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="K90" s="4" t="s">
         <v>635</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>636</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>637</v>
-      </c>
-      <c r="G90" s="2" t="s">
-        <v>638</v>
-      </c>
-      <c r="H90" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I90" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="J90" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="K90" s="4" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="91" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5905,34 +5996,34 @@
         <v>90</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>12</v>
+        <v>491</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D91" s="4" t="s">
+        <v>636</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="J91" s="2" t="s">
         <v>641</v>
       </c>
-      <c r="E91" s="2" t="s">
+      <c r="K91" s="4" t="s">
         <v>642</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="G91" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="H91" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="I91" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="J91" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="K91" s="4" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="92" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5940,34 +6031,34 @@
         <v>91</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>12</v>
+        <v>491</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D92" s="4" t="s">
+        <v>643</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="J92" s="2" t="s">
         <v>648</v>
       </c>
-      <c r="E92" s="2" t="s">
+      <c r="K92" s="4" t="s">
         <v>649</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="G92" s="2" t="s">
-        <v>651</v>
-      </c>
-      <c r="H92" s="2" t="s">
-        <v>652</v>
-      </c>
-      <c r="I92" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="J92" s="2" t="s">
-        <v>653</v>
-      </c>
-      <c r="K92" s="4" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="93" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5975,34 +6066,34 @@
         <v>92</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>12</v>
+        <v>491</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D93" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="I93" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="J93" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="E93" s="2" t="s">
+      <c r="K93" s="4" t="s">
         <v>656</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>657</v>
-      </c>
-      <c r="G93" s="2" t="s">
-        <v>658</v>
-      </c>
-      <c r="H93" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I93" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="J93" s="2" t="s">
-        <v>659</v>
-      </c>
-      <c r="K93" s="4" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="94" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6010,34 +6101,34 @@
         <v>93</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>12</v>
+        <v>491</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>665</v>
+        <v>373</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="K94" s="4" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
     </row>
     <row r="95" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6045,34 +6136,34 @@
         <v>94</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>12</v>
+        <v>491</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>672</v>
+        <v>400</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="K95" s="4" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
     </row>
     <row r="96" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6080,34 +6171,34 @@
         <v>95</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>12</v>
+        <v>491</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D96" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="J96" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="K96" s="4" t="s">
         <v>675</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="F96" s="2" t="s">
-        <v>677</v>
-      </c>
-      <c r="G96" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="H96" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I96" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="J96" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="K96" s="4" t="s">
-        <v>680</v>
       </c>
     </row>
     <row r="97" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6115,34 +6206,34 @@
         <v>96</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>12</v>
+        <v>491</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D97" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="J97" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="E97" s="2" t="s">
+      <c r="K97" s="4" t="s">
         <v>682</v>
-      </c>
-      <c r="F97" s="2" t="s">
-        <v>683</v>
-      </c>
-      <c r="G97" s="2" t="s">
-        <v>684</v>
-      </c>
-      <c r="H97" s="2" t="s">
-        <v>685</v>
-      </c>
-      <c r="I97" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="J97" s="2" t="s">
-        <v>686</v>
-      </c>
-      <c r="K97" s="4" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="98" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6150,34 +6241,34 @@
         <v>97</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>12</v>
+        <v>491</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>445</v>
+        <v>400</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="K98" s="4" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
     </row>
     <row r="99" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6185,34 +6276,34 @@
         <v>98</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>12</v>
+        <v>491</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D99" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="J99" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="E99" s="2" t="s">
+      <c r="K99" s="4" t="s">
         <v>695</v>
-      </c>
-      <c r="F99" s="2" t="s">
-        <v>696</v>
-      </c>
-      <c r="G99" s="2" t="s">
-        <v>697</v>
-      </c>
-      <c r="H99" s="2" t="s">
-        <v>698</v>
-      </c>
-      <c r="I99" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="J99" s="2" t="s">
-        <v>699</v>
-      </c>
-      <c r="K99" s="4" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="100" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6220,34 +6311,34 @@
         <v>99</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D100" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="J100" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="E100" s="2" t="s">
+      <c r="K100" s="4" t="s">
         <v>702</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="G100" s="2" t="s">
-        <v>704</v>
-      </c>
-      <c r="H100" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="I100" s="2" t="s">
-        <v>706</v>
-      </c>
-      <c r="J100" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="K100" s="4" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="101" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6255,34 +6346,34 @@
         <v>100</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>12</v>
+        <v>491</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="K101" s="4" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
     </row>
     <row r="102" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6290,34 +6381,34 @@
         <v>101</v>
       </c>
       <c r="B102" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>709</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="J102" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="K102" s="4" t="s">
         <v>715</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D102" s="4" t="s">
-        <v>716</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>717</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>718</v>
-      </c>
-      <c r="G102" s="2" t="s">
-        <v>719</v>
-      </c>
-      <c r="H102" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I102" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="J102" s="2" t="s">
-        <v>720</v>
-      </c>
-      <c r="K102" s="4" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="103" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6325,34 +6416,34 @@
         <v>102</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>715</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>12</v>
+        <v>491</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>220</v>
+        <v>444</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="K103" s="4" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
     </row>
     <row r="104" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6360,34 +6451,34 @@
         <v>103</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>715</v>
-      </c>
-      <c r="C104" s="3" t="s">
-        <v>12</v>
+        <v>491</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D104" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="I104" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="J104" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="K104" s="4" t="s">
         <v>728</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>729</v>
-      </c>
-      <c r="F104" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="G104" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="H104" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="I104" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="J104" s="2" t="s">
-        <v>733</v>
-      </c>
-      <c r="K104" s="4" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="105" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6395,38 +6486,213 @@
         <v>104</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>715</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>12</v>
+        <v>491</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D105" s="4" t="s">
+        <v>729</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="I105" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="J105" s="2" t="s">
         <v>735</v>
       </c>
-      <c r="E105" s="2" t="s">
+      <c r="K105" s="4" t="s">
         <v>736</v>
       </c>
-      <c r="F105" s="2" t="s">
+    </row>
+    <row r="106" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="2">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D106" s="4" t="s">
         <v>737</v>
       </c>
-      <c r="G105" s="2" t="s">
+      <c r="E106" s="2" t="s">
         <v>738</v>
       </c>
-      <c r="H105" s="2" t="s">
+      <c r="F106" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="H106" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I105" s="2" t="s">
-        <v>739</v>
-      </c>
-      <c r="J105" s="2" t="s">
-        <v>740</v>
-      </c>
-      <c r="K105" s="4" t="s">
+      <c r="I106" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="J106" s="2" t="s">
         <v>741</v>
       </c>
+      <c r="K106" s="4" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="2">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>744</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I107" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="J107" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="K107" s="4" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="2">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>750</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="J108" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="K108" s="4" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="2">
+        <v>108</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>756</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="I109" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="J109" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="K109" s="4" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="2">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>763</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I110" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="J110" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="K110" s="4" t="s">
+        <v>769</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K105"/>
+  <autoFilter ref="A1:K110"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -6441,124 +6707,124 @@
     <col min="2" max="2" width="108" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>742</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>743</v>
+    <row r="1" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>770</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>771</v>
       </c>
     </row>
     <row r="2" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>744</v>
+        <v>772</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>745</v>
+        <v>773</v>
       </c>
     </row>
     <row r="3" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>746</v>
+        <v>774</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>747</v>
+        <v>775</v>
       </c>
     </row>
     <row r="4" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>748</v>
+        <v>776</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>749</v>
+        <v>777</v>
       </c>
     </row>
     <row r="5" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>750</v>
+        <v>778</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>751</v>
+        <v>779</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>752</v>
+        <v>780</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>753</v>
+        <v>781</v>
       </c>
     </row>
     <row r="7" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>754</v>
+        <v>782</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>755</v>
+        <v>783</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>756</v>
+        <v>784</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>757</v>
+        <v>785</v>
       </c>
     </row>
     <row r="9" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>758</v>
+        <v>786</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>759</v>
+        <v>787</v>
       </c>
     </row>
     <row r="10" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>760</v>
+        <v>788</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>761</v>
+        <v>789</v>
       </c>
     </row>
     <row r="11" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>762</v>
+        <v>790</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>763</v>
+        <v>791</v>
       </c>
     </row>
     <row r="12" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>764</v>
+        <v>792</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>765</v>
+        <v>793</v>
       </c>
     </row>
     <row r="13" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>766</v>
+        <v>794</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>767</v>
+        <v>795</v>
       </c>
     </row>
     <row r="14" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>768</v>
+        <v>796</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>769</v>
+        <v>797</v>
       </c>
     </row>
     <row r="15" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>770</v>
+        <v>798</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>771</v>
+        <v>799</v>
       </c>
     </row>
   </sheetData>

--- a/docs/screenshot-index.xlsx
+++ b/docs/screenshot-index.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="905">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="1119">
   <si>
     <t>#</t>
   </si>
@@ -77,6 +77,45 @@
     <t>bom-template-window</t>
   </si>
   <si>
+    <t>editing/pile-editor-half-derived.png</t>
+  </si>
+  <si>
+    <t>The derived half pattern</t>
+  </si>
+  <si>
+    <t>The window on the Half tab before any edit.</t>
+  </si>
+  <si>
+    <t>Click Half table.</t>
+  </si>
+  <si>
+    <t>/docs/editing/piles</t>
+  </si>
+  <si>
+    <t>The Half table tab showing the pattern derived from the full table — same end overhang, even spans — drawn on the half table beside the dashed full outline.</t>
+  </si>
+  <si>
+    <t>pile-editor-half-derived</t>
+  </si>
+  <si>
+    <t>editing/pile-editor-half-full.png</t>
+  </si>
+  <si>
+    <t>The Full tab on a plant with half tables</t>
+  </si>
+  <si>
+    <t>The window on the Full tab with a pattern placed.</t>
+  </si>
+  <si>
+    <t>Generate with Add half tables on, place a pattern, open Piles.</t>
+  </si>
+  <si>
+    <t>The Pile layout window on a plant with half tables: the Full table · Half table switch, the note that half tables follow this pattern, eight piles on the full table and the plant total.</t>
+  </si>
+  <si>
+    <t>pile-editor-half-full</t>
+  </si>
+  <si>
     <t>editing/pile-editor.png</t>
   </si>
   <si>
@@ -89,10 +128,7 @@
     <t>Click Piles: OFF, then Auto grid… and place the piles.</t>
   </si>
   <si>
-    <t>/docs/editing/piles</t>
-  </si>
-  <si>
-    <t>The Pile layout window with an auto grid of eight piles on the reference table, the coordinate table on the left and the Apply to all tables button.</t>
+    <t>The Pile layout window for a plant without half tables: an auto grid of eight piles on one table, the coordinate list on the left, the plant total in the footer and the Apply to all tables button.</t>
   </si>
   <si>
     <t>pile-editor</t>
@@ -419,6 +455,27 @@
     <t>dxf-rendered</t>
   </si>
   <si>
+    <t>exports/export-menu-out-of-date.png</t>
+  </si>
+  <si>
+    <t>The Export menu out of date</t>
+  </si>
+  <si>
+    <t>The menu while the layout is out of date.</t>
+  </si>
+  <si>
+    <t>Change an input after a run, then click Export ▾.</t>
+  </si>
+  <si>
+    <t>/docs/workspace/out-of-date-results</t>
+  </si>
+  <si>
+    <t>The Export menu with the row Inputs changed since the last run. Regenerate first. and every item disabled.</t>
+  </si>
+  <si>
+    <t>export-menu-out-of-date</t>
+  </si>
+  <si>
     <t>exports/export-menu.png</t>
   </si>
   <si>
@@ -434,12 +491,33 @@
     <t>/docs/exports/project-report</t>
   </si>
   <si>
-    <t>The Export menu: Export KMZ, Export DXF, Export ICR-Block DXF, Export Cable Schedule (Excel), Export Detailed Project Report and Export Image (PNG).</t>
+    <t>The Export menu: Export KMZ, Export DXF, Export ICR-Block DXF, Export ICR-Block PDF, Export Cable Schedule (Excel), Export Detailed Project Report and Export Image (PNG).</t>
   </si>
   <si>
     <t>export-menu</t>
   </si>
   <si>
+    <t>exports/icr-blocks-page1.png</t>
+  </si>
+  <si>
+    <t>The ICR-Block PDF: the plant sheet</t>
+  </si>
+  <si>
+    <t>Page one of the ICR-Block PDF.</t>
+  </si>
+  <si>
+    <t>Export ▾ ▸ Export ICR-Block PDF.</t>
+  </si>
+  <si>
+    <t>/docs/layout/icr-blocks</t>
+  </si>
+  <si>
+    <t>Sheet 1 of the ICR-Block PDF: the plant with each block in colour and the ICR BLOCKS table of area, tables, modules, DC, inverters, AC and DC/AC per block.</t>
+  </si>
+  <si>
+    <t>icr-block-pdf-plant</t>
+  </si>
+  <si>
     <t>exports/report-with-piles-page1.png</t>
   </si>
   <si>
@@ -458,6 +536,45 @@
     <t>report-page-drawing</t>
   </si>
   <si>
+    <t>inputs/accb-transformer-group-ond.png</t>
+  </si>
+  <si>
+    <t>The card after a layout</t>
+  </si>
+  <si>
+    <t>The card after loading an OND and generating.</t>
+  </si>
+  <si>
+    <t>Load an OND, generate, then open the Electrical tab.</t>
+  </si>
+  <si>
+    <t>/docs/inputs/accb-and-transformers</t>
+  </si>
+  <si>
+    <t>The ACCB &amp; Transformer card after a layout with an inverter file: LV voltage 800 V from the OND and the answer line Now: 12 ACCBs · 5 transformers: 4 × 10,000 + 1 × 16,000 kVA.</t>
+  </si>
+  <si>
+    <t>accb-transformer-group-ond</t>
+  </si>
+  <si>
+    <t>inputs/accb-transformer-group.png</t>
+  </si>
+  <si>
+    <t>The ACCB &amp; Transformer card</t>
+  </si>
+  <si>
+    <t>The card before an inverter file and a layout.</t>
+  </si>
+  <si>
+    <t>Electrical tab, nothing loaded.</t>
+  </si>
+  <si>
+    <t>The ACCB &amp; Transformer card at its defaults: inverters per ACCB, ACCBs per transformer, transformer size limit, the standard transformer ratings, MV voltage, the power transformer margin, derating and ratings, and the LV voltage line.</t>
+  </si>
+  <si>
+    <t>accb-transformer-group</t>
+  </si>
+  <si>
     <t>inputs/boundary-file-card.png</t>
   </si>
   <si>
@@ -569,7 +686,7 @@
     <t>Electrical tab, nothing changed.</t>
   </si>
   <si>
-    <t>The Cables card at its defaults: Calculate cables unticked, inter-module lead, the string return run tick, and the DC cable slack.</t>
+    <t>The Cables card at its defaults: Calculate cables unticked, inter-module lead 0.00 m/module, the string return run unticked, and DC cable slack 10.0 %.</t>
   </si>
   <si>
     <t>cables-group</t>
@@ -581,21 +698,39 @@
     <t>Site reference for a CAD drawing</t>
   </si>
   <si>
-    <t>The window as it opens for a .dxf or .dwg file.</t>
-  </si>
-  <si>
-    <t>Browse to a CAD file.</t>
+    <t>The window for a local-coordinate .dxf with a latitude and longitude typed in.</t>
+  </si>
+  <si>
+    <t>Browse to a .dxf drawn in local coordinates and type the site centre's latitude and longitude.</t>
   </si>
   <si>
     <t>/docs/inputs/cad-boundary</t>
   </si>
   <si>
-    <t>The Site reference window for a CAD file: the I know the site coordinates tick, latitude and longitude, the consequence banner, and the Layout only and Use this location buttons.</t>
+    <t>The Site reference window for a drawing in local coordinates: Place by latitude and longitude chosen, latitude and longitude filled in, the Placed by hand banner and the Place the drawing here button.</t>
   </si>
   <si>
     <t>dxf-site-coordinates</t>
   </si>
   <si>
+    <t>inputs/dxf-site-utm.png</t>
+  </si>
+  <si>
+    <t>A drawing in UTM coordinates</t>
+  </si>
+  <si>
+    <t>The window for a UTM-shaped .dxf.</t>
+  </si>
+  <si>
+    <t>Browse to a .dxf drawn in UTM coordinates and pick its zone.</t>
+  </si>
+  <si>
+    <t>The Site reference window for a drawing whose coordinates look like UTM: the Drawing's coordinates option with a UTM zone chosen and the Use UTM zone 42N button.</t>
+  </si>
+  <si>
+    <t>dxf-site-utm</t>
+  </si>
+  <si>
     <t>inputs/image-scale.png</t>
   </si>
   <si>
@@ -611,7 +746,7 @@
     <t>/docs/inputs/image-boundary</t>
   </si>
   <si>
-    <t>The Site reference window for an image: the SCALE card reading 100.00 m on site is drawn as 10.00 mm with the 1 : 10,000 hint, then the LOCATION card.</t>
+    <t>The Site reference window for an image: the SCALE card reading 100.00 m on site is drawn as 10.00 mm, then the LOCATION card with nothing filled in.</t>
   </si>
   <si>
     <t>image-scale</t>
@@ -986,12 +1121,30 @@
     <t>/docs/first-layout</t>
   </si>
   <si>
-    <t>The main window after a fixed-tilt run on the sample site: the placed tables, control rooms and inverters on the plot, the Tools tab unlocked, and the plant chips filled in.</t>
+    <t>The main window after a fixed-tilt run on the sample site: the placed tables, control rooms and inverters on the plot, and the plant chips filled in.</t>
   </si>
   <si>
     <t>layout-fixed-tilt</t>
   </si>
   <si>
+    <t>layout/icr-block-summary.png</t>
+  </si>
+  <si>
+    <t>An ICR block summary window</t>
+  </si>
+  <si>
+    <t>The window for one block.</t>
+  </si>
+  <si>
+    <t>With ICR blocks on, click a block.</t>
+  </si>
+  <si>
+    <t>The ICR-1 — Demo window: tiles for DC capacity, tables, modules and string inverters, then block area, perimeter, ACCBs, transformer, transformer load, inverter and AC capacity, DC/AC ratio, cable lengths, arresters and piles, with PDF…, Copy and Close.</t>
+  </si>
+  <si>
+    <t>icr-block-summary</t>
+  </si>
+  <si>
     <t>layout/icr-blocks.png</t>
   </si>
   <si>
@@ -1007,7 +1160,7 @@
     <t>/docs/layout/icr</t>
   </si>
   <si>
-    <t>The Layout view with the ICR blocks layer on: each block's area filled in its own colour with its outline drawn.</t>
+    <t>The Layout view with the ICR blocks layer on: each block — the tables wired to one ICR — filled in its own colour with its outline drawn.</t>
   </si>
   <si>
     <t>icr-blocks</t>
@@ -1043,7 +1196,7 @@
     <t>/docs/workspace/views</t>
   </si>
   <si>
-    <t>The row of plant chips under the view: DC capacity, site area, tables, modules, ICR blocks and year-one P50 energy.</t>
+    <t>The row of plant chips under the view, led by a Design warnings chip: DC capacity, site area, tables, modules, ICR blocks, lightning arresters and year-one P50 energy.</t>
   </si>
   <si>
     <t>kpi-strip</t>
@@ -1331,12 +1484,108 @@
     <t>/docs/simulation/ac-capacity</t>
   </si>
   <si>
-    <t>The Simulation with AC Capacity window: the TARGET and EQUIPMENT cards on the left; on the right the verdict Fits this layout, the capacity meter and the result tiles, and the Regenerate layout button.</t>
+    <t>The Simulation with AC Capacity window: the TARGET and EQUIPMENT cards on the left; on the right the verdict Fits this layout, the capacity meter, the result tiles and the ICR block AC row, and the Regenerate layout button.</t>
   </si>
   <si>
     <t>ac-capacity</t>
   </si>
   <si>
+    <t>simulation/earthing-boq.png</t>
+  </si>
+  <si>
+    <t>The BoQ tab</t>
+  </si>
+  <si>
+    <t>The window on the BoQ tab.</t>
+  </si>
+  <si>
+    <t>Click BoQ.</t>
+  </si>
+  <si>
+    <t>/docs/simulation/earthing</t>
+  </si>
+  <si>
+    <t>The BoQ tab of Earthing Design: S.No, Description, Qty, Unit and Remark for the strips, cable, pits and accessories.</t>
+  </si>
+  <si>
+    <t>earthing-boq</t>
+  </si>
+  <si>
+    <t>simulation/earthing-calculation.png</t>
+  </si>
+  <si>
+    <t>The Calculation tab</t>
+  </si>
+  <si>
+    <t>The window on the Calculation tab.</t>
+  </si>
+  <si>
+    <t>Click Calculation.</t>
+  </si>
+  <si>
+    <t>The Calculation tab of Earthing Design: the numbered calculation report with the design basis and each step.</t>
+  </si>
+  <si>
+    <t>earthing-calculation</t>
+  </si>
+  <si>
+    <t>simulation/earthing-layout.png</t>
+  </si>
+  <si>
+    <t>Earthing Design</t>
+  </si>
+  <si>
+    <t>The window on the Layout tab at the defaults.</t>
+  </si>
+  <si>
+    <t>Generate, then Tools ▸ Earthing Design….</t>
+  </si>
+  <si>
+    <t>The Earthing Design window: the verdict 284 earth pits · plant grid 0.11 Ω (target ≤ 1 Ω), the Soil &amp; site and Fault data inputs on the left, and the Layout tab drawing the conductors and earth pits over the plant with its legend.</t>
+  </si>
+  <si>
+    <t>earthing-layout</t>
+  </si>
+  <si>
+    <t>simulation/robot-dxf-gaps.png</t>
+  </si>
+  <si>
+    <t>The Gaps view</t>
+  </si>
+  <si>
+    <t>The window on Gaps with some gaps ticked.</t>
+  </si>
+  <si>
+    <t>Click Gaps and tick the gaps you will bridge.</t>
+  </si>
+  <si>
+    <t>/docs/simulation/robot-count-from-dxf</t>
+  </si>
+  <si>
+    <t>The Gaps view: the wide gaps listed by filter with three ticked for bridging, and the verdict counting the bridges.</t>
+  </si>
+  <si>
+    <t>robot-dxf-gaps</t>
+  </si>
+  <si>
+    <t>simulation/robot-dxf.png</t>
+  </si>
+  <si>
+    <t>Robot count from DXF</t>
+  </si>
+  <si>
+    <t>The window after reading a drawing.</t>
+  </si>
+  <si>
+    <t>Tools ▸ Robot count from DXF…, then Open DXF….</t>
+  </si>
+  <si>
+    <t>The Robot count from DXF window with a plant drawing read: the DRAWING and ROBOT cards and the verdict on the left, the four tiles and the Layout view of the drawing with its gaps on the right, and Export PDF….</t>
+  </si>
+  <si>
+    <t>robot-dxf</t>
+  </si>
+  <si>
     <t>simulation/robotic-cleaning.png</t>
   </si>
   <si>
@@ -1364,7 +1613,7 @@
     <t>The Studies card</t>
   </si>
   <si>
-    <t>The Studies card with Simulation with AC Capacity, Robotic Module Cleaning and Shadow View (row spacing).</t>
+    <t>The Studies card with five buttons: Simulation with AC Capacity, Robotic Module Cleaning, Robot count from DXF…, Shadow View (row spacing) and Earthing Design.</t>
   </si>
   <si>
     <t>studies</t>
@@ -1496,7 +1745,7 @@
     <t>Generate, then click Tools.</t>
   </si>
   <si>
-    <t>The main window showing the Tools tab with the Obstructions, Main Control Room &amp; Objects and Studies cards enabled, over a generated layout.</t>
+    <t>The main window on the Tools tab after a layout: the Obstructions card, the ICR tip, Main Control Room &amp; Objects and the five Studies buttons, with the placed MCR's hint.</t>
   </si>
   <si>
     <t>tab-tools</t>
@@ -1580,6 +1829,24 @@
     <t>energy-view</t>
   </si>
   <si>
+    <t>views/out-of-date.png</t>
+  </si>
+  <si>
+    <t>A layout that is out of date</t>
+  </si>
+  <si>
+    <t>The whole window on the Layout view after an input changed.</t>
+  </si>
+  <si>
+    <t>Generate, then change the module wattage and the perimeter road width.</t>
+  </si>
+  <si>
+    <t>The main window after two inputs changed: Regenerate Layout with 2 inputs changed since the last run, amber dots on the Site and Array tabs, the changed field in amber, the Out of date note over the dimmed plot, and the Out of date chip.</t>
+  </si>
+  <si>
+    <t>out-of-date</t>
+  </si>
+  <si>
     <t>views/sld-auto.png</t>
   </si>
   <si>
@@ -1595,7 +1862,7 @@
     <t>/docs/sld/auto-build</t>
   </si>
   <si>
-    <t>The SLD view after Generate: Automatic, with the annotated chain PV array, string inverters, ACCB, transformers, switchgear and grid on the sheet.</t>
+    <t>The SLD view after Generate: Automatic, with the annotated chain PV array, string inverters, ACCBs, inverter duty transformers, switchgear and grid on the sheet.</t>
   </si>
   <si>
     <t>sld-auto</t>
@@ -1619,6 +1886,27 @@
     <t>sld-blank</t>
   </si>
   <si>
+    <t>views/summary-design-warnings.png</t>
+  </si>
+  <si>
+    <t>Design warnings in the Summary view</t>
+  </si>
+  <si>
+    <t>The whole window on the Summary view with two warnings.</t>
+  </si>
+  <si>
+    <t>Tick Calculate cables, set ICR Block to 60 MWp, generate, then click Summary.</t>
+  </si>
+  <si>
+    <t>/docs/reference/design-warnings</t>
+  </si>
+  <si>
+    <t>The Summary view with the 2 design warnings banner: 78 AC feeders drop more than 2.5 % and the plant's LV AC drop averages 2.25 %, over the 1.5 % budget; the Design warnings chip reads 2.</t>
+  </si>
+  <si>
+    <t>summary-design-warnings</t>
+  </si>
+  <si>
     <t>views/summary-multi-plot.png</t>
   </si>
   <si>
@@ -1670,7 +1958,7 @@
     <t>Click Summary.</t>
   </si>
   <si>
-    <t>The Summary view: a Metric column and one column for the plant, grouped under SITE, ARRAY, ELECTRICAL, CABLES and ENERGY.</t>
+    <t>The Summary view: a Metric column and one column for the plant, grouped under SITE, ARRAY, ELECTRICAL and CABLES, with the ACCBs, Transformers (IDT) and Power transformer (MVA) rows.</t>
   </si>
   <si>
     <t>summary-view</t>
@@ -1691,6 +1979,60 @@
     <t>bom-tools</t>
   </si>
   <si>
+    <t>editing/pile-editor-half-changed.png</t>
+  </si>
+  <si>
+    <t>A half pattern made for an earlier full pattern</t>
+  </si>
+  <si>
+    <t>The Full tab after the full pattern changed under an own half pattern.</t>
+  </si>
+  <si>
+    <t>Change the full pattern after making an own half pattern.</t>
+  </si>
+  <si>
+    <t>The Full tab with the warning Half tables use your own pattern, made for an earlier full table, and the Review button.</t>
+  </si>
+  <si>
+    <t>pile-editor-half-changed</t>
+  </si>
+  <si>
+    <t>editing/pile-editor-half-own.png</t>
+  </si>
+  <si>
+    <t>An own half pattern</t>
+  </si>
+  <si>
+    <t>The Half tab after editing the pattern.</t>
+  </si>
+  <si>
+    <t>On the Half tab, place piles with Auto grid….</t>
+  </si>
+  <si>
+    <t>The Half table tab after an auto grid: the note Your own pattern for half tables and the Reset to derived button.</t>
+  </si>
+  <si>
+    <t>pile-editor-half-own</t>
+  </si>
+  <si>
+    <t>editing/pile-editor-half-tracker.png</t>
+  </si>
+  <si>
+    <t>A half tracker's derived pattern</t>
+  </si>
+  <si>
+    <t>The Half tab in a tracker design.</t>
+  </si>
+  <si>
+    <t>Generate a tracker design with Add half trackers on, place a pattern, click Half tracker.</t>
+  </si>
+  <si>
+    <t>The Half tracker tab of the Pile layout window: the derived pattern with a drive pile at the centre of the half tracker.</t>
+  </si>
+  <si>
+    <t>pile-editor-half-tracker</t>
+  </si>
+  <si>
     <t>editing/piles-layout-off.png</t>
   </si>
   <si>
@@ -1811,12 +2153,45 @@
     <t>Apply a pile pattern, then click Export ▾.</t>
   </si>
   <si>
-    <t>The Export menu with the extra Export PDF (with Piles) item shown because the pile overlay is on.</t>
+    <t>The Export menu with the extra Export PDF (with Piles) item, shown while the pile overlay is on.</t>
   </si>
   <si>
     <t>export-menu-piles</t>
   </si>
   <si>
+    <t>exports/icr-blocks-page2.png</t>
+  </si>
+  <si>
+    <t>The ICR-Block PDF: a block sheet</t>
+  </si>
+  <si>
+    <t>Page two of the ICR-Block PDF.</t>
+  </si>
+  <si>
+    <t>A block sheet of the ICR-Block PDF: the block drawn with its key plan and the BLOCK DETAILS table.</t>
+  </si>
+  <si>
+    <t>icr-block-pdf-block</t>
+  </si>
+  <si>
+    <t>exports/report-warnings-page2.png</t>
+  </si>
+  <si>
+    <t>Design warnings on the PDF summary page</t>
+  </si>
+  <si>
+    <t>Page two of the PDF with piles, exported with two warnings.</t>
+  </si>
+  <si>
+    <t>Export PDF (with Piles) with the warnings present.</t>
+  </si>
+  <si>
+    <t>The PDF report's summary page carrying the DESIGN WARNINGS block with each warning's plant, check and finding.</t>
+  </si>
+  <si>
+    <t>report-page-warnings</t>
+  </si>
+  <si>
     <t>exports/report-with-piles-page2.png</t>
   </si>
   <si>
@@ -1907,6 +2282,24 @@
     <t>cables-group-on</t>
   </si>
   <si>
+    <t>inputs/dxf-site-layout-only.png</t>
+  </si>
+  <si>
+    <t>Layout only</t>
+  </si>
+  <si>
+    <t>The window with Layout only chosen.</t>
+  </si>
+  <si>
+    <t>Browse to a .dxf and choose Layout only.</t>
+  </si>
+  <si>
+    <t>The Site reference window with Layout only chosen: an optional latitude for tilt and row pitch, the banner on what is not available, and the Continue with layout only button.</t>
+  </si>
+  <si>
+    <t>dxf-site-layout-only</t>
+  </si>
+  <si>
     <t>inputs/ond-efficiency-curve.png</t>
   </si>
   <si>
@@ -2102,6 +2495,24 @@
     <t>expanded-view</t>
   </si>
   <si>
+    <t>layout/icr-block-selected.png</t>
+  </si>
+  <si>
+    <t>A block selected from the keyboard</t>
+  </si>
+  <si>
+    <t>The whole window with one block selected.</t>
+  </si>
+  <si>
+    <t>Switch ICR blocks on, click the plot, then press an arrow key.</t>
+  </si>
+  <si>
+    <t>The Layout view with the ICR blocks layer on and ICR-1 outlined as the keyboard selection; the status bar reads ICR-1 selected — press Enter to open its summary.</t>
+  </si>
+  <si>
+    <t>icr-block-selected</t>
+  </si>
+  <si>
     <t>layout/kpi-strip-energy.png</t>
   </si>
   <si>
@@ -2210,6 +2621,93 @@
     <t>wireframe</t>
   </si>
   <si>
+    <t>projects/reopened.png</t>
+  </si>
+  <si>
+    <t>A reopened project</t>
+  </si>
+  <si>
+    <t>The whole window straight after opening a saved project.</t>
+  </si>
+  <si>
+    <t>Save a project after Generate, then open it in a new window.</t>
+  </si>
+  <si>
+    <t>The main window after Open Project: the saved layout on the plot, the view tools enabled and the status Opened Demo.slp · the layout matches its inputs.</t>
+  </si>
+  <si>
+    <t>reopened</t>
+  </si>
+  <si>
+    <t>simulation/ac-capacity-icr-block.png</t>
+  </si>
+  <si>
+    <t>ICR block AC set</t>
+  </si>
+  <si>
+    <t>The window with ICR block AC filled in.</t>
+  </si>
+  <si>
+    <t>Type an AC capacity per block into ICR block AC.</t>
+  </si>
+  <si>
+    <t>The Simulation with AC Capacity window with ICR block AC set to 18600 kW and the hint → 2 blocks of 24.180 MWp DC.</t>
+  </si>
+  <si>
+    <t>ac-capacity-icr-block</t>
+  </si>
+  <si>
+    <t>simulation/earthing-warn.png</t>
+  </si>
+  <si>
+    <t>A target the grid does not meet</t>
+  </si>
+  <si>
+    <t>The window with a target below the plant grid's resistance.</t>
+  </si>
+  <si>
+    <t>Set Targets ▸ Whole plant below the computed grid value.</t>
+  </si>
+  <si>
+    <t>Earthing Design with a whole-plant target of 0.10 Ω, which the plant grid does not meet: the verdict turns to a warning.</t>
+  </si>
+  <si>
+    <t>earthing-warn</t>
+  </si>
+  <si>
+    <t>simulation/robot-dxf-layers.png</t>
+  </si>
+  <si>
+    <t>The Layers view</t>
+  </si>
+  <si>
+    <t>The window on Layers.</t>
+  </si>
+  <si>
+    <t>Click Layers.</t>
+  </si>
+  <si>
+    <t>The Layers view: every layer of the drawing with the role guessed from its name, editable in a list.</t>
+  </si>
+  <si>
+    <t>robot-dxf-layers</t>
+  </si>
+  <si>
+    <t>simulation/tools-menu.png</t>
+  </si>
+  <si>
+    <t>The Tools menu</t>
+  </si>
+  <si>
+    <t>Click Tools in the menu bar.</t>
+  </si>
+  <si>
+    <t>The Tools menu with Robot count from DXF… and Earthing Design….</t>
+  </si>
+  <si>
+    <t>tools-menu</t>
+  </si>
+  <si>
     <t>sld/symbol-editor.png</t>
   </si>
   <si>
@@ -2315,7 +2813,7 @@
     <t>Click Electrical.</t>
   </si>
   <si>
-    <t>The main window showing the Electrical tab: the String Inverter card and the Cables card.</t>
+    <t>The main window on the Electrical tab: the String Inverter card, the ACCB &amp; Transformer card and the Cables card.</t>
   </si>
   <si>
     <t>tab-electrical-window</t>
@@ -2333,7 +2831,7 @@
     <t>Click Tools before generating.</t>
   </si>
   <si>
-    <t>The main window showing the Tools tab with every button greyed out because no layout exists yet.</t>
+    <t>The main window on the Tools tab before a layout: every button greyed out except Robot count from DXF…, which needs no layout.</t>
   </si>
   <si>
     <t>tab-tools-locked</t>
@@ -2390,10 +2888,64 @@
     <t>help-menu</t>
   </si>
   <si>
+    <t>views/bom-design-warnings.png</t>
+  </si>
+  <si>
+    <t>Design warnings in the BOM</t>
+  </si>
+  <si>
+    <t>The whole window on the BOM view with two warnings.</t>
+  </si>
+  <si>
+    <t>As for the Summary with design warnings, then click BOM.</t>
+  </si>
+  <si>
+    <t>The BOM view with the AC Cable (Inverter → ICR) row tinted and carrying a Check: remark for the feeder-drop warning.</t>
+  </si>
+  <si>
+    <t>bom-design-warnings</t>
+  </si>
+  <si>
+    <t>views/kpi-strip-warnings.png</t>
+  </si>
+  <si>
+    <t>The Design warnings chip</t>
+  </si>
+  <si>
+    <t>The chip row with two warnings.</t>
+  </si>
+  <si>
+    <t>As for the Summary with design warnings.</t>
+  </si>
+  <si>
+    <t>The plant chips led by the Design warnings chip reading 2.</t>
+  </si>
+  <si>
+    <t>kpi-strip-warnings</t>
+  </si>
+  <si>
+    <t>views/out-of-date-changes.png</t>
+  </si>
+  <si>
+    <t>The list of changes</t>
+  </si>
+  <si>
+    <t>The popover opened from Show 2 changes.</t>
+  </si>
+  <si>
+    <t>Click Show 2 changes on the Out of date note.</t>
+  </si>
+  <si>
+    <t>The Changed since the last run list naming each changed input with its value at the last run.</t>
+  </si>
+  <si>
+    <t>out-of-date-changes</t>
+  </si>
+  <si>
     <t>views/sld-auto-full.png</t>
   </si>
   <si>
-    <t>The full per-ICR diagram</t>
+    <t>The full per-feeder diagram</t>
   </si>
   <si>
     <t>The whole window with the Full SLD option on.</t>
@@ -2402,12 +2954,30 @@
     <t>Tick Full SLD (per-ICR / per-feeder).</t>
   </si>
   <si>
-    <t>The SLD view with Full SLD (per-ICR / per-feeder) ticked, showing parallel feeders converging on per-ICR transformers.</t>
+    <t>The SLD view with Full SLD (per-ICR / per-feeder) ticked, showing one feeder row per ACCB grouped by transformer.</t>
   </si>
   <si>
     <t>sld-auto-full</t>
   </si>
   <si>
+    <t>views/summary-out-of-date.png</t>
+  </si>
+  <si>
+    <t>The Summary view out of date</t>
+  </si>
+  <si>
+    <t>The whole window on the Summary view while out of date.</t>
+  </si>
+  <si>
+    <t>Change an input after a run, then click Summary.</t>
+  </si>
+  <si>
+    <t>The Summary view with its out-of-date banner above the figures from the last run.</t>
+  </si>
+  <si>
+    <t>summary-out-of-date</t>
+  </si>
+  <si>
     <t>views/summary-window.png</t>
   </si>
   <si>
@@ -2462,6 +3032,24 @@
     <t>yield-group-central</t>
   </si>
   <si>
+    <t>exports/earthing-page1.png</t>
+  </si>
+  <si>
+    <t>The earthing report</t>
+  </si>
+  <si>
+    <t>Page one of the exported report.</t>
+  </si>
+  <si>
+    <t>Click Export PDF report….</t>
+  </si>
+  <si>
+    <t>Page one of the earthing PDF report.</t>
+  </si>
+  <si>
+    <t>earthing-pdf</t>
+  </si>
+  <si>
     <t>exports/report-with-piles-page4.png</t>
   </si>
   <si>
@@ -2480,6 +3068,42 @@
     <t>report-page-bom</t>
   </si>
   <si>
+    <t>exports/robot-count-page1.png</t>
+  </si>
+  <si>
+    <t>The robot count PDF</t>
+  </si>
+  <si>
+    <t>Page one of the exported PDF.</t>
+  </si>
+  <si>
+    <t>Click Export PDF….</t>
+  </si>
+  <si>
+    <t>Page one of the robot count PDF: the answer, the inputs and the plan.</t>
+  </si>
+  <si>
+    <t>robot-dxf-pdf</t>
+  </si>
+  <si>
+    <t>layout/icr-block-out-of-date.png</t>
+  </si>
+  <si>
+    <t>A block window out of date</t>
+  </si>
+  <si>
+    <t>The window opened while the layout is out of date.</t>
+  </si>
+  <si>
+    <t>Change an input after a run, then click a block.</t>
+  </si>
+  <si>
+    <t>An ICR block summary window with its out-of-date banner and PDF… and Copy disabled.</t>
+  </si>
+  <si>
+    <t>icr-block-out-of-date</t>
+  </si>
+  <si>
     <t>layout/kpi-strip-multi.png</t>
   </si>
   <si>
@@ -2601,6 +3225,24 @@
   </si>
   <si>
     <t>edit-pile-menu</t>
+  </si>
+  <si>
+    <t>simulation/robot-dxf-rows.png</t>
+  </si>
+  <si>
+    <t>The Rows view</t>
+  </si>
+  <si>
+    <t>The window on Rows.</t>
+  </si>
+  <si>
+    <t>Click Rows.</t>
+  </si>
+  <si>
+    <t>The Rows view: each cleaning line with its tables, segments, longest segment and robots, beside a verdict of 234 robots with 3 bridges.</t>
+  </si>
+  <si>
+    <t>robot-dxf-rows</t>
   </si>
   <si>
     <t>views/summary-tracker-central.png</t>
@@ -3133,7 +3775,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K140"/>
+  <dimension ref="A1:K175"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -3315,13 +3957,13 @@
         <v>17</v>
       </c>
       <c r="I5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3335,28 +3977,28 @@
         <v>12</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J6" s="2" t="s">
+      <c r="K6" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3370,28 +4012,28 @@
         <v>12</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="H7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3405,28 +4047,28 @@
         <v>12</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3440,28 +4082,28 @@
         <v>12</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="K9" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3475,28 +4117,28 @@
         <v>12</v>
       </c>
       <c r="D10" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="H10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="J10" s="2" t="s">
+      <c r="K10" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3510,28 +4152,28 @@
         <v>12</v>
       </c>
       <c r="D11" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="H11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I11" s="2" t="s">
+      <c r="J11" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="K11" s="4" t="s">
         <v>76</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3545,28 +4187,28 @@
         <v>12</v>
       </c>
       <c r="D12" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="G12" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="H12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I12" s="2" t="s">
+      <c r="K12" s="4" t="s">
         <v>82</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3580,28 +4222,28 @@
         <v>12</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="G13" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="H13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="J13" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="J13" s="2" t="s">
+      <c r="K13" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3615,13 +4257,13 @@
         <v>12</v>
       </c>
       <c r="D14" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>73</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>93</v>
@@ -3665,13 +4307,13 @@
         <v>17</v>
       </c>
       <c r="I15" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="J15" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="K15" s="4" t="s">
         <v>102</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3685,28 +4327,28 @@
         <v>12</v>
       </c>
       <c r="D16" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="H16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="J16" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="H16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="J16" s="2" t="s">
+      <c r="K16" s="4" t="s">
         <v>108</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3720,28 +4362,28 @@
         <v>12</v>
       </c>
       <c r="D17" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="G17" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="H17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="H17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I17" s="2" t="s">
+      <c r="J17" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="K17" s="4" t="s">
         <v>115</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3755,13 +4397,13 @@
         <v>12</v>
       </c>
       <c r="D18" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>73</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>119</v>
@@ -3770,7 +4412,7 @@
         <v>17</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>120</v>
@@ -3805,13 +4447,13 @@
         <v>17</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3825,13 +4467,13 @@
         <v>12</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>131</v>
@@ -3840,13 +4482,13 @@
         <v>17</v>
       </c>
       <c r="I20" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J20" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="J20" s="2" t="s">
+      <c r="K20" s="4" t="s">
         <v>133</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="21" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3860,28 +4502,28 @@
         <v>12</v>
       </c>
       <c r="D21" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="G21" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="H21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="J21" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="H21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I21" s="2" t="s">
+      <c r="K21" s="4" t="s">
         <v>139</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="22" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3895,28 +4537,28 @@
         <v>12</v>
       </c>
       <c r="D22" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="G22" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="H22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="J22" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="H22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="J22" s="2" t="s">
+      <c r="K22" s="4" t="s">
         <v>146</v>
-      </c>
-      <c r="K22" s="4" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="23" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3930,28 +4572,28 @@
         <v>12</v>
       </c>
       <c r="D23" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="G23" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="H23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="H23" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I23" s="2" t="s">
+      <c r="J23" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="J23" s="2" t="s">
+      <c r="K23" s="4" t="s">
         <v>153</v>
-      </c>
-      <c r="K23" s="4" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="24" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3965,22 +4607,22 @@
         <v>12</v>
       </c>
       <c r="D24" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="G24" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="H24" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>158</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>152</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>159</v>
@@ -4050,7 +4692,7 @@
         <v>17</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>172</v>
@@ -4190,13 +4832,13 @@
         <v>17</v>
       </c>
       <c r="I30" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="J30" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="J30" s="2" t="s">
+      <c r="K30" s="4" t="s">
         <v>199</v>
-      </c>
-      <c r="K30" s="4" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="31" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4210,28 +4852,28 @@
         <v>12</v>
       </c>
       <c r="D31" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="F31" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="G31" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="H31" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="H31" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I31" s="2" t="s">
+      <c r="J31" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="J31" s="2" t="s">
+      <c r="K31" s="4" t="s">
         <v>206</v>
-      </c>
-      <c r="K31" s="4" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4245,28 +4887,28 @@
         <v>12</v>
       </c>
       <c r="D32" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="F32" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="G32" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="H32" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="J32" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="H32" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="J32" s="2" t="s">
+      <c r="K32" s="4" t="s">
         <v>212</v>
-      </c>
-      <c r="K32" s="4" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="33" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4280,13 +4922,13 @@
         <v>12</v>
       </c>
       <c r="D33" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="F33" s="2" t="s">
         <v>215</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>183</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>216</v>
@@ -4356,22 +4998,22 @@
         <v>227</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>183</v>
+        <v>228</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="36" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4385,22 +5027,22 @@
         <v>12</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>237</v>
@@ -4435,13 +5077,13 @@
         <v>17</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="38" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4455,28 +5097,28 @@
         <v>12</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="39" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4490,28 +5132,28 @@
         <v>12</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>124</v>
+        <v>255</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>228</v>
+        <v>256</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="40" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4525,28 +5167,28 @@
         <v>12</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>259</v>
+        <v>222</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>217</v>
+        <v>262</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="41" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4560,28 +5202,28 @@
         <v>12</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>229</v>
+        <v>262</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="42" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4595,28 +5237,28 @@
         <v>12</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>271</v>
+        <v>222</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>101</v>
+        <v>274</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="43" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4630,28 +5272,28 @@
         <v>12</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>183</v>
+        <v>279</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="44" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4665,28 +5307,28 @@
         <v>12</v>
       </c>
       <c r="D44" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I44" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>283</v>
-      </c>
       <c r="J44" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="45" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4700,28 +5342,28 @@
         <v>12</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="46" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4735,28 +5377,28 @@
         <v>12</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>295</v>
+        <v>136</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="47" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4770,28 +5412,28 @@
         <v>12</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>297</v>
+        <v>262</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="48" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4805,28 +5447,28 @@
         <v>12</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>310</v>
+        <v>274</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4840,28 +5482,28 @@
         <v>12</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>310</v>
+        <v>113</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="50" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4875,13 +5517,13 @@
         <v>12</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>321</v>
+        <v>222</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>322</v>
@@ -4916,22 +5558,22 @@
         <v>327</v>
       </c>
       <c r="F51" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I51" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="G51" s="2" t="s">
+      <c r="J51" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="H51" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I51" s="2" t="s">
+      <c r="K51" s="4" t="s">
         <v>330</v>
-      </c>
-      <c r="J51" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="K51" s="4" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="52" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4945,22 +5587,22 @@
         <v>12</v>
       </c>
       <c r="D52" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="F52" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="E52" s="2" t="s">
+      <c r="G52" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="F52" s="2" t="s">
+      <c r="H52" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I52" s="2" t="s">
         <v>335</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>330</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>336</v>
@@ -5100,7 +5742,7 @@
         <v>17</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>310</v>
+        <v>355</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>362</v>
@@ -5135,13 +5777,13 @@
         <v>17</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="58" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5155,22 +5797,22 @@
         <v>12</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>374</v>
+        <v>165</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>375</v>
@@ -5196,22 +5838,22 @@
         <v>378</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>353</v>
+        <v>379</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>354</v>
+        <v>380</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="60" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5225,28 +5867,28 @@
         <v>12</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>385</v>
+        <v>354</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="61" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5260,28 +5902,28 @@
         <v>12</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="62" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5295,28 +5937,28 @@
         <v>12</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>283</v>
+        <v>393</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="63" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5330,28 +5972,28 @@
         <v>12</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K63" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="64" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5365,28 +6007,28 @@
         <v>12</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="65" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5400,22 +6042,22 @@
         <v>12</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>419</v>
@@ -5450,13 +6092,13 @@
         <v>17</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K66" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="67" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5470,28 +6112,28 @@
         <v>12</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="G67" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I67" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="H67" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I67" s="2" t="s">
+      <c r="J67" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="J67" s="2" t="s">
+      <c r="K67" s="4" t="s">
         <v>432</v>
-      </c>
-      <c r="K67" s="4" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="68" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5505,28 +6147,28 @@
         <v>12</v>
       </c>
       <c r="D68" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="E68" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="E68" s="2" t="s">
+      <c r="F68" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="F68" s="2" t="s">
+      <c r="G68" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="G68" s="2" t="s">
+      <c r="H68" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="J68" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="H68" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I68" s="2" t="s">
+      <c r="K68" s="4" t="s">
         <v>438</v>
-      </c>
-      <c r="J68" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="K68" s="4" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="69" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5540,28 +6182,28 @@
         <v>12</v>
       </c>
       <c r="D69" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="F69" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="E69" s="2" t="s">
+      <c r="G69" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="F69" s="2" t="s">
+      <c r="H69" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I69" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="G69" s="2" t="s">
+      <c r="J69" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="H69" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I69" s="2" t="s">
+      <c r="K69" s="4" t="s">
         <v>445</v>
-      </c>
-      <c r="J69" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="K69" s="4" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="70" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5575,22 +6217,22 @@
         <v>12</v>
       </c>
       <c r="D70" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="F70" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="E70" s="2" t="s">
+      <c r="G70" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="F70" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>354</v>
-      </c>
       <c r="H70" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>438</v>
+        <v>328</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>450</v>
@@ -5660,7 +6302,7 @@
         <v>17</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>323</v>
+        <v>393</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>463</v>
@@ -5730,7 +6372,7 @@
         <v>17</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>405</v>
+        <v>469</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>476</v>
@@ -5765,13 +6407,13 @@
         <v>17</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="76" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5785,28 +6427,28 @@
         <v>12</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>323</v>
+        <v>489</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="77" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5820,28 +6462,28 @@
         <v>12</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>469</v>
+        <v>496</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="78" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5855,28 +6497,28 @@
         <v>12</v>
       </c>
       <c r="D78" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I78" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="E78" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="G78" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I78" s="2" t="s">
-        <v>500</v>
-      </c>
       <c r="J78" s="2" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="79" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5890,28 +6532,28 @@
         <v>12</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>507</v>
+        <v>496</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="80" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5925,28 +6567,28 @@
         <v>12</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>101</v>
+        <v>515</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="81" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5960,28 +6602,28 @@
         <v>12</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>101</v>
+        <v>515</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="82" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5995,28 +6637,28 @@
         <v>12</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="83" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6030,22 +6672,22 @@
         <v>12</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>531</v>
+        <v>404</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>455</v>
+        <v>405</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>532</v>
+        <v>489</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>533</v>
@@ -6080,13 +6722,13 @@
         <v>17</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>374</v>
+        <v>539</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="K84" s="4" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="85" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6100,22 +6742,22 @@
         <v>12</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>545</v>
+        <v>368</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>546</v>
@@ -6150,13 +6792,13 @@
         <v>17</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>342</v>
+        <v>552</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="K86" s="4" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="87" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6164,7 +6806,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>554</v>
+        <v>11</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>12</v>
@@ -6176,22 +6818,22 @@
         <v>556</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>454</v>
+        <v>557</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>506</v>
+        <v>558</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>507</v>
+        <v>456</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="K87" s="4" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="88" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6199,34 +6841,34 @@
         <v>87</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>554</v>
+        <v>11</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>25</v>
+        <v>552</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="K88" s="4" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="89" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6234,34 +6876,34 @@
         <v>88</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>554</v>
+        <v>11</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>569</v>
+        <v>368</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="K89" s="4" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="90" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6269,34 +6911,34 @@
         <v>89</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>554</v>
+        <v>11</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>569</v>
+        <v>552</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="K90" s="4" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="91" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6304,34 +6946,34 @@
         <v>90</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>554</v>
+        <v>11</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>569</v>
+        <v>583</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="K91" s="4" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="92" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6339,34 +6981,34 @@
         <v>91</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>554</v>
+        <v>11</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>81</v>
+        <v>589</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>82</v>
+        <v>590</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="K92" s="4" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
     </row>
     <row r="93" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6374,34 +7016,34 @@
         <v>92</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>554</v>
+        <v>11</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>507</v>
+        <v>113</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="K93" s="4" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
     </row>
     <row r="94" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6409,34 +7051,34 @@
         <v>93</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>554</v>
+        <v>11</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>25</v>
+        <v>113</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="K94" s="4" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
     </row>
     <row r="95" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6444,34 +7086,34 @@
         <v>94</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>554</v>
+        <v>11</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="K95" s="4" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
     </row>
     <row r="96" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6479,34 +7121,34 @@
         <v>95</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>554</v>
+        <v>11</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="K96" s="4" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
     </row>
     <row r="97" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6514,34 +7156,34 @@
         <v>96</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>554</v>
+        <v>11</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>617</v>
+        <v>538</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>611</v>
+        <v>621</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="K97" s="4" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
     </row>
     <row r="98" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6549,34 +7191,34 @@
         <v>97</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>554</v>
+        <v>11</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>204</v>
+        <v>627</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>178</v>
+        <v>628</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="K98" s="4" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
     </row>
     <row r="99" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6584,34 +7226,34 @@
         <v>98</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>554</v>
+        <v>11</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>178</v>
+        <v>425</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="K99" s="4" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
     </row>
     <row r="100" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6619,34 +7261,34 @@
         <v>99</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>554</v>
+        <v>11</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>205</v>
+        <v>641</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="K100" s="4" t="s">
-        <v>636</v>
+        <v>643</v>
       </c>
     </row>
     <row r="101" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6654,34 +7296,34 @@
         <v>100</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>554</v>
+        <v>11</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>205</v>
+        <v>393</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="K101" s="4" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
     </row>
     <row r="102" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6689,34 +7331,34 @@
         <v>101</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>554</v>
+        <v>650</v>
       </c>
       <c r="C102" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>645</v>
+        <v>537</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>646</v>
+        <v>589</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>205</v>
+        <v>590</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="K102" s="4" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
     </row>
     <row r="103" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6724,34 +7366,34 @@
         <v>102</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>554</v>
+        <v>650</v>
       </c>
       <c r="C103" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>217</v>
+        <v>25</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="K103" s="4" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
     </row>
     <row r="104" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6759,34 +7401,34 @@
         <v>103</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>554</v>
+        <v>650</v>
       </c>
       <c r="C104" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>645</v>
+        <v>663</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>217</v>
+        <v>25</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>658</v>
+        <v>665</v>
       </c>
       <c r="K104" s="4" t="s">
-        <v>659</v>
+        <v>666</v>
       </c>
     </row>
     <row r="105" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6794,34 +7436,34 @@
         <v>104</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>554</v>
+        <v>650</v>
       </c>
       <c r="C105" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>297</v>
+        <v>25</v>
       </c>
       <c r="J105" s="2" t="s">
-        <v>664</v>
+        <v>671</v>
       </c>
       <c r="K105" s="4" t="s">
-        <v>665</v>
+        <v>672</v>
       </c>
     </row>
     <row r="106" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6829,34 +7471,34 @@
         <v>105</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>554</v>
+        <v>650</v>
       </c>
       <c r="C106" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>668</v>
+        <v>675</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>94</v>
+        <v>25</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="K106" s="4" t="s">
-        <v>671</v>
+        <v>678</v>
       </c>
     </row>
     <row r="107" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6864,34 +7506,34 @@
         <v>106</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>554</v>
+        <v>650</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>672</v>
+        <v>679</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>675</v>
+        <v>682</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>283</v>
+        <v>683</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="K107" s="4" t="s">
-        <v>677</v>
+        <v>685</v>
       </c>
     </row>
     <row r="108" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6899,34 +7541,34 @@
         <v>107</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>554</v>
+        <v>650</v>
       </c>
       <c r="C108" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>679</v>
+        <v>687</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>680</v>
+        <v>688</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>297</v>
+        <v>683</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>682</v>
+        <v>690</v>
       </c>
       <c r="K108" s="4" t="s">
-        <v>683</v>
+        <v>691</v>
       </c>
     </row>
     <row r="109" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6934,34 +7576,34 @@
         <v>108</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>554</v>
+        <v>650</v>
       </c>
       <c r="C109" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>686</v>
+        <v>694</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>310</v>
+        <v>683</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="K109" s="4" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
     </row>
     <row r="110" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6969,34 +7611,34 @@
         <v>109</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>554</v>
+        <v>650</v>
       </c>
       <c r="C110" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>693</v>
+        <v>93</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>342</v>
+        <v>94</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="K110" s="4" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
     </row>
     <row r="111" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7004,34 +7646,34 @@
         <v>110</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>554</v>
+        <v>650</v>
       </c>
       <c r="C111" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>342</v>
+        <v>590</v>
       </c>
       <c r="J111" s="2" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="K111" s="4" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
     </row>
     <row r="112" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7039,34 +7681,34 @@
         <v>111</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>554</v>
+        <v>650</v>
       </c>
       <c r="C112" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>342</v>
+        <v>25</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="K112" s="4" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
     </row>
     <row r="113" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7074,34 +7716,34 @@
         <v>112</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>554</v>
+        <v>650</v>
       </c>
       <c r="C113" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>711</v>
+        <v>164</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>379</v>
+        <v>165</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="K113" s="4" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
     </row>
     <row r="114" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7109,34 +7751,34 @@
         <v>113</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>554</v>
+        <v>650</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>374</v>
+        <v>628</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="K114" s="4" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
     </row>
     <row r="115" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7144,34 +7786,34 @@
         <v>114</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>554</v>
+        <v>650</v>
       </c>
       <c r="C115" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>342</v>
+        <v>158</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="K115" s="4" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
     </row>
     <row r="116" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7179,34 +7821,34 @@
         <v>115</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>554</v>
+        <v>650</v>
       </c>
       <c r="C116" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>392</v>
+        <v>736</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="K116" s="4" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
     </row>
     <row r="117" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7214,22 +7856,22 @@
         <v>116</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>554</v>
+        <v>650</v>
       </c>
       <c r="C117" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>17</v>
@@ -7238,10 +7880,10 @@
         <v>736</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="K117" s="4" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
     </row>
     <row r="118" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7249,34 +7891,34 @@
         <v>117</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>554</v>
+        <v>650</v>
       </c>
       <c r="C118" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>742</v>
+        <v>249</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>405</v>
+        <v>217</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="K118" s="4" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
     </row>
     <row r="119" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7284,34 +7926,34 @@
         <v>118</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>554</v>
+        <v>650</v>
       </c>
       <c r="C119" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>374</v>
+        <v>217</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="K119" s="4" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
     </row>
     <row r="120" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7319,34 +7961,34 @@
         <v>119</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>554</v>
+        <v>650</v>
       </c>
       <c r="C120" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>405</v>
+        <v>230</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="K120" s="4" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
     </row>
     <row r="121" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7354,34 +7996,34 @@
         <v>120</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>554</v>
+        <v>650</v>
       </c>
       <c r="C121" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>469</v>
+        <v>250</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="K121" s="4" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
     </row>
     <row r="122" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7389,34 +8031,34 @@
         <v>121</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>554</v>
+        <v>650</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>469</v>
+        <v>250</v>
       </c>
       <c r="J122" s="2" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
       <c r="K122" s="4" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
     </row>
     <row r="123" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7424,34 +8066,34 @@
         <v>122</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>554</v>
+        <v>650</v>
       </c>
       <c r="C123" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>769</v>
+        <v>774</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>469</v>
+        <v>250</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="K123" s="4" t="s">
-        <v>774</v>
+        <v>779</v>
       </c>
     </row>
     <row r="124" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7459,34 +8101,34 @@
         <v>123</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>554</v>
+        <v>650</v>
       </c>
       <c r="C124" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>777</v>
+        <v>782</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>469</v>
+        <v>262</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="K124" s="4" t="s">
-        <v>780</v>
+        <v>785</v>
       </c>
     </row>
     <row r="125" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7494,34 +8136,34 @@
         <v>124</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>554</v>
+        <v>650</v>
       </c>
       <c r="C125" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>500</v>
+        <v>262</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="K125" s="4" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
     </row>
     <row r="126" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7529,34 +8171,34 @@
         <v>125</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>554</v>
+        <v>650</v>
       </c>
       <c r="C126" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>429</v>
+        <v>793</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>500</v>
+        <v>342</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="K126" s="4" t="s">
-        <v>791</v>
+        <v>796</v>
       </c>
     </row>
     <row r="127" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7564,34 +8206,34 @@
         <v>126</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>554</v>
+        <v>650</v>
       </c>
       <c r="C127" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I127" s="2" t="s">
-        <v>526</v>
+        <v>106</v>
       </c>
       <c r="J127" s="2" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="K127" s="4" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
     </row>
     <row r="128" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7599,34 +8241,34 @@
         <v>127</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>554</v>
+        <v>650</v>
       </c>
       <c r="C128" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>798</v>
+        <v>803</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>799</v>
+        <v>804</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>801</v>
+        <v>806</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>545</v>
+        <v>328</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>802</v>
+        <v>807</v>
       </c>
       <c r="K128" s="4" t="s">
-        <v>803</v>
+        <v>808</v>
       </c>
     </row>
     <row r="129" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7634,34 +8276,34 @@
         <v>128</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>804</v>
+        <v>650</v>
       </c>
       <c r="C129" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I129" s="2" t="s">
-        <v>38</v>
+        <v>342</v>
       </c>
       <c r="J129" s="2" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="K129" s="4" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
     </row>
     <row r="130" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7669,34 +8311,34 @@
         <v>129</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>804</v>
+        <v>650</v>
       </c>
       <c r="C130" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>622</v>
+        <v>817</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I130" s="2" t="s">
-        <v>94</v>
+        <v>355</v>
       </c>
       <c r="J130" s="2" t="s">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="K130" s="4" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
     </row>
     <row r="131" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7704,34 +8346,34 @@
         <v>130</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>804</v>
+        <v>650</v>
       </c>
       <c r="C131" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>816</v>
+        <v>821</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>817</v>
+        <v>822</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>818</v>
+        <v>823</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>819</v>
+        <v>824</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I131" s="2" t="s">
-        <v>139</v>
+        <v>393</v>
       </c>
       <c r="J131" s="2" t="s">
-        <v>820</v>
+        <v>825</v>
       </c>
       <c r="K131" s="4" t="s">
-        <v>821</v>
+        <v>826</v>
       </c>
     </row>
     <row r="132" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7739,34 +8381,34 @@
         <v>131</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>804</v>
+        <v>650</v>
       </c>
       <c r="C132" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>822</v>
+        <v>827</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>823</v>
+        <v>828</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>824</v>
+        <v>829</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>825</v>
+        <v>830</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I132" s="2" t="s">
-        <v>374</v>
+        <v>165</v>
       </c>
       <c r="J132" s="2" t="s">
-        <v>826</v>
+        <v>831</v>
       </c>
       <c r="K132" s="4" t="s">
-        <v>827</v>
+        <v>832</v>
       </c>
     </row>
     <row r="133" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7774,34 +8416,34 @@
         <v>132</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>804</v>
+        <v>650</v>
       </c>
       <c r="C133" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>829</v>
+        <v>834</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I133" s="2" t="s">
-        <v>310</v>
+        <v>393</v>
       </c>
       <c r="J133" s="2" t="s">
-        <v>832</v>
+        <v>837</v>
       </c>
       <c r="K133" s="4" t="s">
-        <v>833</v>
+        <v>838</v>
       </c>
     </row>
     <row r="134" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7809,34 +8451,34 @@
         <v>133</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>804</v>
+        <v>650</v>
       </c>
       <c r="C134" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>836</v>
+        <v>841</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I134" s="2" t="s">
-        <v>342</v>
+        <v>393</v>
       </c>
       <c r="J134" s="2" t="s">
-        <v>838</v>
+        <v>843</v>
       </c>
       <c r="K134" s="4" t="s">
-        <v>839</v>
+        <v>844</v>
       </c>
     </row>
     <row r="135" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7844,34 +8486,34 @@
         <v>134</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>804</v>
+        <v>650</v>
       </c>
       <c r="C135" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>840</v>
+        <v>845</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>841</v>
+        <v>846</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>842</v>
+        <v>847</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I135" s="2" t="s">
-        <v>283</v>
+        <v>430</v>
       </c>
       <c r="J135" s="2" t="s">
-        <v>844</v>
+        <v>849</v>
       </c>
       <c r="K135" s="4" t="s">
-        <v>845</v>
+        <v>850</v>
       </c>
     </row>
     <row r="136" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7879,34 +8521,34 @@
         <v>135</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>804</v>
+        <v>650</v>
       </c>
       <c r="C136" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>846</v>
+        <v>851</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>847</v>
+        <v>852</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>849</v>
+        <v>854</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I136" s="2" t="s">
-        <v>355</v>
+        <v>425</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>850</v>
+        <v>855</v>
       </c>
       <c r="K136" s="4" t="s">
-        <v>851</v>
+        <v>856</v>
       </c>
     </row>
     <row r="137" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7914,34 +8556,34 @@
         <v>136</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>804</v>
+        <v>650</v>
       </c>
       <c r="C137" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I137" s="2" t="s">
-        <v>25</v>
+        <v>393</v>
       </c>
       <c r="J137" s="2" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="K137" s="4" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
     </row>
     <row r="138" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7949,34 +8591,34 @@
         <v>137</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>804</v>
+        <v>650</v>
       </c>
       <c r="C138" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>858</v>
+        <v>863</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>859</v>
+        <v>864</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>429</v>
+        <v>865</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>860</v>
+        <v>866</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I138" s="2" t="s">
-        <v>25</v>
+        <v>443</v>
       </c>
       <c r="J138" s="2" t="s">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="K138" s="4" t="s">
-        <v>862</v>
+        <v>868</v>
       </c>
     </row>
     <row r="139" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7984,34 +8626,34 @@
         <v>138</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>804</v>
+        <v>650</v>
       </c>
       <c r="C139" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>865</v>
+        <v>871</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>866</v>
+        <v>872</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I139" s="2" t="s">
-        <v>545</v>
+        <v>482</v>
       </c>
       <c r="J139" s="2" t="s">
-        <v>867</v>
+        <v>873</v>
       </c>
       <c r="K139" s="4" t="s">
-        <v>868</v>
+        <v>874</v>
       </c>
     </row>
     <row r="140" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8019,38 +8661,1263 @@
         <v>139</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>804</v>
+        <v>650</v>
       </c>
       <c r="C140" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>869</v>
+        <v>875</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>870</v>
+        <v>876</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>871</v>
+        <v>877</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>872</v>
+        <v>878</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I140" s="2" t="s">
-        <v>101</v>
+        <v>489</v>
       </c>
       <c r="J140" s="2" t="s">
-        <v>873</v>
+        <v>879</v>
       </c>
       <c r="K140" s="4" t="s">
-        <v>874</v>
+        <v>880</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="2">
+        <v>140</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D141" s="4" t="s">
+        <v>881</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="F141" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I141" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="J141" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="K141" s="4" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="2">
+        <v>141</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D142" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="F142" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="G142" s="2" t="s">
+        <v>890</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I142" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="J142" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="K142" s="4" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="2">
+        <v>142</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D143" s="4" t="s">
+        <v>893</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="F143" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="G143" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I143" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="J143" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="K143" s="4" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="2">
+        <v>143</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D144" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>899</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>900</v>
+      </c>
+      <c r="G144" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I144" s="2" t="s">
+        <v>902</v>
+      </c>
+      <c r="J144" s="2" t="s">
+        <v>903</v>
+      </c>
+      <c r="K144" s="4" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="2">
+        <v>144</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D145" s="4" t="s">
+        <v>905</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="F145" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="G145" s="2" t="s">
+        <v>908</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I145" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="J145" s="2" t="s">
+        <v>909</v>
+      </c>
+      <c r="K145" s="4" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="2">
+        <v>145</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D146" s="4" t="s">
+        <v>911</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>913</v>
+      </c>
+      <c r="G146" s="2" t="s">
+        <v>914</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I146" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="J146" s="2" t="s">
+        <v>915</v>
+      </c>
+      <c r="K146" s="4" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="2">
+        <v>146</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D147" s="4" t="s">
+        <v>917</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="F147" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="G147" s="2" t="s">
+        <v>920</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I147" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="J147" s="2" t="s">
+        <v>921</v>
+      </c>
+      <c r="K147" s="4" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="2">
+        <v>147</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D148" s="4" t="s">
+        <v>923</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>924</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>926</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I148" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="J148" s="2" t="s">
+        <v>927</v>
+      </c>
+      <c r="K148" s="4" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="2">
+        <v>148</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D149" s="4" t="s">
+        <v>929</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>930</v>
+      </c>
+      <c r="F149" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="G149" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I149" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="J149" s="2" t="s">
+        <v>933</v>
+      </c>
+      <c r="K149" s="4" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="2">
+        <v>149</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D150" s="4" t="s">
+        <v>935</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="F150" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="G150" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I150" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="J150" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="K150" s="4" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="2">
+        <v>150</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D151" s="4" t="s">
+        <v>941</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="F151" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="G151" s="2" t="s">
+        <v>944</v>
+      </c>
+      <c r="H151" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I151" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="J151" s="2" t="s">
+        <v>945</v>
+      </c>
+      <c r="K151" s="4" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="2">
+        <v>151</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D152" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>948</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>949</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>950</v>
+      </c>
+      <c r="H152" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I152" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="J152" s="2" t="s">
+        <v>951</v>
+      </c>
+      <c r="K152" s="4" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="2">
+        <v>152</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D153" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>954</v>
+      </c>
+      <c r="F153" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="H153" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I153" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="J153" s="2" t="s">
+        <v>956</v>
+      </c>
+      <c r="K153" s="4" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="2">
+        <v>153</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D154" s="4" t="s">
+        <v>958</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="F154" s="2" t="s">
+        <v>960</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>961</v>
+      </c>
+      <c r="H154" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I154" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="J154" s="2" t="s">
+        <v>962</v>
+      </c>
+      <c r="K154" s="4" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="2">
+        <v>154</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D155" s="4" t="s">
+        <v>964</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>965</v>
+      </c>
+      <c r="F155" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="G155" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="H155" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I155" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="J155" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="K155" s="4" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="2">
+        <v>155</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D156" s="4" t="s">
+        <v>970</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="F156" s="2" t="s">
+        <v>972</v>
+      </c>
+      <c r="G156" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="H156" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I156" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="J156" s="2" t="s">
+        <v>974</v>
+      </c>
+      <c r="K156" s="4" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="2">
+        <v>156</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D157" s="4" t="s">
+        <v>976</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="F157" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="G157" s="2" t="s">
+        <v>979</v>
+      </c>
+      <c r="H157" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I157" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="J157" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="K157" s="4" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="2">
+        <v>157</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D158" s="4" t="s">
+        <v>982</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>983</v>
+      </c>
+      <c r="F158" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="G158" s="2" t="s">
+        <v>985</v>
+      </c>
+      <c r="H158" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I158" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="J158" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="K158" s="4" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="2">
+        <v>158</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D159" s="4" t="s">
+        <v>988</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>989</v>
+      </c>
+      <c r="F159" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>991</v>
+      </c>
+      <c r="H159" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I159" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="J159" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="K159" s="4" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="2">
+        <v>159</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D160" s="4" t="s">
+        <v>995</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="H160" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I160" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J160" s="2" t="s">
+        <v>999</v>
+      </c>
+      <c r="K160" s="4" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="2">
+        <v>160</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D161" s="4" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>1002</v>
+      </c>
+      <c r="F161" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="G161" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="H161" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I161" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J161" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="K161" s="4" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="2">
+        <v>161</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D162" s="4" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F162" s="2" t="s">
+        <v>1008</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>1009</v>
+      </c>
+      <c r="H162" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I162" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="J162" s="2" t="s">
+        <v>1010</v>
+      </c>
+      <c r="K162" s="4" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="2">
+        <v>162</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D163" s="4" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="F163" s="2" t="s">
+        <v>1014</v>
+      </c>
+      <c r="G163" s="2" t="s">
+        <v>1015</v>
+      </c>
+      <c r="H163" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I163" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="J163" s="2" t="s">
+        <v>1016</v>
+      </c>
+      <c r="K163" s="4" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="2">
+        <v>163</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D164" s="4" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="F164" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="G164" s="2" t="s">
+        <v>1021</v>
+      </c>
+      <c r="H164" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I164" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="J164" s="2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="K164" s="4" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="2">
+        <v>164</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D165" s="4" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>1026</v>
+      </c>
+      <c r="G165" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H165" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I165" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="J165" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="K165" s="4" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="2">
+        <v>165</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D166" s="4" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F166" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="G166" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="H166" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I166" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="J166" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="K166" s="4" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="2">
+        <v>166</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D167" s="4" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="G167" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="H167" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I167" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="J167" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="K167" s="4" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="2">
+        <v>167</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D168" s="4" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="F168" s="2" t="s">
+        <v>1044</v>
+      </c>
+      <c r="G168" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="H168" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I168" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="J168" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="K168" s="4" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A169" s="2">
+        <v>168</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D169" s="4" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="F169" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="G169" s="2" t="s">
+        <v>1051</v>
+      </c>
+      <c r="H169" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I169" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="J169" s="2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="K169" s="4" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A170" s="2">
+        <v>169</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D170" s="4" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F170" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="G170" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="H170" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I170" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="J170" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K170" s="4" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="2">
+        <v>170</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="C171" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D171" s="4" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F171" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="G171" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="H171" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I171" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J171" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="K171" s="4" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A172" s="2">
+        <v>171</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D172" s="4" t="s">
+        <v>1066</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="F172" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="G172" s="2" t="s">
+        <v>1068</v>
+      </c>
+      <c r="H172" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I172" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J172" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="K172" s="4" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A173" s="2">
+        <v>172</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="C173" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D173" s="4" t="s">
+        <v>1071</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>1072</v>
+      </c>
+      <c r="F173" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="G173" s="2" t="s">
+        <v>1074</v>
+      </c>
+      <c r="H173" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I173" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="J173" s="2" t="s">
+        <v>1075</v>
+      </c>
+      <c r="K173" s="4" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A174" s="2">
+        <v>173</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D174" s="4" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>1078</v>
+      </c>
+      <c r="F174" s="2" t="s">
+        <v>1079</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>1080</v>
+      </c>
+      <c r="H174" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I174" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="J174" s="2" t="s">
+        <v>1081</v>
+      </c>
+      <c r="K174" s="4" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A175" s="2">
+        <v>174</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D175" s="4" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="F175" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="G175" s="2" t="s">
+        <v>1086</v>
+      </c>
+      <c r="H175" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I175" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="J175" s="2" t="s">
+        <v>1087</v>
+      </c>
+      <c r="K175" s="4" t="s">
+        <v>1088</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K140"/>
+  <autoFilter ref="A1:K175"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -8067,122 +9934,122 @@
   <sheetData>
     <row r="1" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>875</v>
+        <v>1089</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>876</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="2" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>877</v>
+        <v>1091</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>878</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="3" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>879</v>
+        <v>1093</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>880</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="4" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>881</v>
+        <v>1095</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>882</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="5" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>883</v>
+        <v>1097</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>884</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>885</v>
+        <v>1099</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>886</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="7" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>887</v>
+        <v>1101</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>888</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>889</v>
+        <v>1103</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>890</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="9" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>891</v>
+        <v>1105</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>892</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="10" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>893</v>
+        <v>1107</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>894</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="11" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>895</v>
+        <v>1109</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>896</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="12" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>897</v>
+        <v>1111</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>898</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="13" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>899</v>
+        <v>1113</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>900</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="14" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>901</v>
+        <v>1115</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>902</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="15" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>903</v>
+        <v>1117</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>904</v>
+        <v>1118</v>
       </c>
     </row>
   </sheetData>
